--- a/documentation/Automation Vetify.xlsx
+++ b/documentation/Automation Vetify.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ikeasistenciaarg-my.sharepoint.com/personal/lpicinotti_ikeasistencia_com_ar/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="11_58CBC5BC44333993AE15EA8AD8BEC47FAAC1BC36" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9811AB3-5BEE-48E4-B8BF-7279E947E579}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929DFDDE-F32E-4095-8CAA-1179C3EEE175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roadmap QA Automation" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="408">
   <si>
     <t>ID</t>
   </si>
@@ -869,9 +869,6 @@
     <t xml:space="preserve">Ver elon boarding la primera vez que se logue en cualquier ya sea mobile o desktop </t>
   </si>
   <si>
-    <t xml:space="preserve">Tour onboarding </t>
-  </si>
-  <si>
     <t xml:space="preserve">Tour onboarding en segundo logueo  </t>
   </si>
   <si>
@@ -908,9 +905,6 @@
     <t xml:space="preserve">06. Historial de Atención </t>
   </si>
   <si>
-    <t>Videollamada</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cancelar turno ya agendado </t>
   </si>
   <si>
@@ -945,6 +939,330 @@
   </si>
   <si>
     <t>Alta  - capitado osde</t>
+  </si>
+  <si>
+    <t>QA-AUTO-080</t>
+  </si>
+  <si>
+    <t>QA-AUTO-081</t>
+  </si>
+  <si>
+    <t>QA-AUTO-082</t>
+  </si>
+  <si>
+    <t>QA-AUTO-083</t>
+  </si>
+  <si>
+    <t>Incluye TS-01 a TS-07 de Flujo de Compra (compra exitosa, fallida, asociacion con usuario existente, cupones, formulario pasos 1-3). 19/31 CPs automatizados. Principal freno: TS-04 Cupones (1/7) por falta de un cupon de prueba real en el ambiente de QA -- es un tema de datos/negocio, no de codigo.</t>
+  </si>
+  <si>
+    <t>Incluye TS-01 a TS-07. 16/31 CPs automatizados. Mismo freno de cupon que B2C (TS-04, 1/7). Pendiente de confirmar: TS-01 (compra exitosa) figura 0/8 en Casos de Prueba.xlsx, pero hoy (29/08) hay un test real de compra exitosa para OSDE Adquirente que corre y pasa -- posible desactualizacion del tracker tactico, no de este roadmap.</t>
+  </si>
+  <si>
+    <t>5/5 CPs automatizados (TS-01 Proceso de Compra + TS-02 Validacion de formulario).</t>
+  </si>
+  <si>
+    <t>5/5 CPs automatizados, pero la unica cuenta del pool tageada Flux Capitado resulto ser un producto OSDE real bajo la etiqueta equivocada (ver qa-workspace/known-issues.md). El 100% no confirma todavia cobertura del sub-segmento Flux genuino.</t>
+  </si>
+  <si>
+    <t>Gestion de Usuario, bloque Adquirentes OSDE, TS-01 Registracion: 5/5 CPs automatizados.</t>
+  </si>
+  <si>
+    <t>Gestion de Usuario, bloque Capitado OSDE, TS-01 Registracion: 5/5 CPs automatizados.</t>
+  </si>
+  <si>
+    <t>TS-01 Registracion CP-04 (Registracion exitosa) -- patron identico automatizado en los 4 productos (B2C, Adquirente OSDE, Capitado OSDE, Capitado Flux).</t>
+  </si>
+  <si>
+    <t>TS-01 Registracion CP-01 (Email ya existente) -- automatizado en los 4 productos.</t>
+  </si>
+  <si>
+    <t>TS-01 Registracion CP-02 (Contrasena debil) + CP-05 (Campos obligatorios) -- automatizados en los 4 productos.</t>
+  </si>
+  <si>
+    <t>TS-03 Activacion de Cuenta completo: 5/5 CPs automatizados (campos obligatorios, tipos de documento, documento no existente/ya registrado, activacion exitosa).</t>
+  </si>
+  <si>
+    <t>Cubierto implicitamente por TS-01 CP-04 (Registracion exitosa, incluye setear contrasena valida). No hay un CP dedicado solo a crear contrasena, pero el camino feliz esta probado.</t>
+  </si>
+  <si>
+    <t>TS-01 Registracion CP-02 (Contrasena debil) -- automatizado.</t>
+  </si>
+  <si>
+    <t>TS-02 Iniciar Sesion CP-03 (Email y contrasena correcta) -- automatizado.</t>
+  </si>
+  <si>
+    <t>TS-02 Iniciar Sesion CP-01 (Contrasena incorrecta) + CP-02 (Email no existente) -- automatizados.</t>
+  </si>
+  <si>
+    <t>Incluye 2 sub-flujos con estados distintos: solicitar el reset (TS-04 IMAS-3215, 5/5 automatizado) funciona; completar el cambio via el link (TS-05 Cambio de Contrasena, 0/5) esta bloqueado por el problema de rate-limit/invalidacion de ticket documentado 2026-08-29. 5/10 CPs combinados.</t>
+  </si>
+  <si>
+    <t>TS-04 Olvide contrasena CP-03 (Negativo, email no registrado) -- automatizado.</t>
+  </si>
+  <si>
+    <t>Gap real: no existe un CP dedicado a cambiar contrasena desde un usuario ya autenticado (distinto del reseteo via email) en ninguna hoja de Casos de Prueba.xlsx revisada hasta ahora (Flujo de Compra, Gestion de Usuario, Perfil).</t>
+  </si>
+  <si>
+    <t>Mismo gap que la fila anterior -- no hay CP de cambio de contrasena logueado, por lo tanto tampoco de su variante de rechazo.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay un CP dedicado a Logout en ninguna hoja revisada. Nota aparte: existe un bug conocido de logout en Prestadores (BUG-008, Auth0 no cierra sesion) pero es un hallazgo puntual, no una suite de casos de Logout general.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP de acceso a contenido protegido tras logout en las hojas revisadas.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP de persistencia de sesion ante refresh en las hojas revisadas.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay ningun CP de Tour de onboarding en Casos de Prueba.xlsx todavia -- funcionalidad nunca disenada como caso de prueba.</t>
+  </si>
+  <si>
+    <t>Mismo gap que la fila anterior.</t>
+  </si>
+  <si>
+    <t>Hoja Perfil, CP Visualizacion del perfil -- automatizado (desktop y mobile).</t>
+  </si>
+  <si>
+    <t>Hoja Perfil: cambiar foto (automatizado) y actualizar telefono (automatizado) SI estan cubiertos. Cambiar DNI es el punto debil: 2 de 4 CPs ni siquiera estan escritos todavia (marcados DBD en el Excel tactico) y los otros 2 estan escritos pero no automatizados. 2/6 CPs reales automatizados.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP dedicado a ver el detalle completo de una mascota (datos, plan, servicios asociados) en ninguna hoja revisada.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP dedicado a cambiar la mascota activa/contexto. Existe un selector de mascota en otras pantallas (ej. videollamada) pero sin CP propio de este comportamiento.</t>
+  </si>
+  <si>
+    <t>Hoja Credenciales, TS-01 Visualizacion de Planes (4/4) + TS-04 Ver Credenciales (2/2) -- 6/6 CPs automatizados.</t>
+  </si>
+  <si>
+    <t>Hoja Credenciales, TS-03 Crear Credencial, CP-01 (cargar con foto) -- automatizado. CP-02 (cargar sin foto) esta marcado [Obsoleto] en el Excel tactico, excluido del calculo.</t>
+  </si>
+  <si>
+    <t>Hoja Credenciales, TS-02 Cargar credencial - Validacion de Pasos, subconjunto de navegacion/campos (18 CPs, excluyendo los 5 de camara/formato/tamano que se cuentan en la fila de errores) -- 18/18 automatizados.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP dedicado al disparo de la encuesta de experiencia (CE) post carga de credencial en ninguna hoja revisada.</t>
+  </si>
+  <si>
+    <t>Hoja Credenciales, TS-02, subconjunto de errores (columna Automatizado Desktop): fecha futura (No), camara no disponible (No), camara disponible (No -- limitacion real de dispositivo, no gap de automatizacion), formato invalido (Si), imagen demasiado grande (Si). 2/5 CPs en desktop. Aparte: el mismo caso de imagen demasiado grande tiene un test MOBILE escrito el 2026-08-29 pero todavia sin verificar en vivo (columna Automatizado Mobile de esta misma hoja sigue en No) -- no afecta este numero, que es solo desktop.</t>
+  </si>
+  <si>
+    <t>Hoja Videollamadas, combinando IMAS-3899 (5 de 5, bloqueo sin credencial), IMAS-3174 (8 de 8, flujo 1 mascota), IMAS-3889 (17 de 18, multi-mascota y adjuntos, unico No es un caso de bypass de validacion directo a API), IMAS-3909 (4 de 4, limites de turnos) e IMAS-4023 (4 de 4, errores de carga de archivo, excluyendo 1 CP marcado Fuera de alcance). 38 de 39 CPs.</t>
+  </si>
+  <si>
+    <t>Los 2 CPs relacionados (IMAS-3894 CP05 y CP06) estan marcados explicitamente como Brecha de cobertura y Fuera de alcance en Casos de Prueba.xlsx -- salir de la videoconsulta (sala de espera, ingreso y salida) fue una decision ya tomada de no automatizar, no un gap pendiente de priorizar.</t>
+  </si>
+  <si>
+    <t>Mismo caso que la fila anterior (IMAS-3894 CP05 y CP06, Brecha de cobertura y Fuera de alcance) -- ingresar a la videoconsulta en si (mas alla del turno agendado) fue decision de no automatizar, no gap pendiente.</t>
+  </si>
+  <si>
+    <t>Hoja Videollamadas, IMAS-3894 CP08, caso de Regresion: la assistanceId vieja no ofrece acciones habilitadas tras reprogramar -- automatizado.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP de refresh de pagina durante una videollamada activa en ninguna hoja revisada.</t>
+  </si>
+  <si>
+    <t>Gap real: el unico negativo relacionado (IMAS-3899 CP05, backend rechaza turno sin credencial) ya esta contado en la fila de Solicitar videollamada -- no hay CP de error o indisponibilidad del servicio de videollamada en si.</t>
+  </si>
+  <si>
+    <t>Hoja Videollamadas, IMAS-3894 CP03: cancelacion con doble check -- automatizado.</t>
+  </si>
+  <si>
+    <t>Revisado tras encontrar la hoja Misceláneas: CP-01 (Mobile) confirma ver al menos una mascota en Mis mascotas -- automatizado. Sumado a la evidencia indirecta ya vista en Credenciales (plan con y sin mascota asociada). Sigue siendo smoke test (ve al menos una), no valida el detalle completo del listado, pero ya no es un gap de tracking como se penso antes de revisar esta hoja.</t>
+  </si>
+  <si>
+    <t>Gap en el tracker tactico: no existe una hoja de Casos de Prueba.xlsx dedicada a validaciones de backend Salesforce o Engage. Nota importante: el codigo de Flujo de Compra (VetifyCheckoutPage.completePersonalData) SI valida partes del payload enviado a la API de Salesforce como parte del test de compra, pero eso no esta documentado como CP propio -- posible cobertura parcial no trackeada, requiere revision dedicada antes de confirmar un numero distinto de 0.</t>
+  </si>
+  <si>
+    <t>Hoja Miscelaneas, CP-04 (Mobile): ve las tarjetas de Emergencias y Asistencia presencial en Servicios -- automatizado.</t>
+  </si>
+  <si>
+    <t>Hoja Miscelaneas, CP-04 (Mobile): ve las tarjetas de Emergencias y Asistencia presencial en Servicios -- automatizado (mismo CP que Emergencias).</t>
+  </si>
+  <si>
+    <t>Hoja Miscelaneas, CP-08 (Mobile): Llamanos por telefono abre el marcador del sistema -- automatizado.</t>
+  </si>
+  <si>
+    <t>Hoja Miscelaneas, CP-06 (Mobile): muestra la historia clinica de una mascota -- automatizado.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay ningun CP sobre el mapa de prestadores o veterinarias en ninguna hoja de Casos de Prueba.xlsx (incluyendo Miscelaneas, que no lo menciona).</t>
+  </si>
+  <si>
+    <t>Hoja Miscelaneas, CP-02 (Mobile): ve al menos un plan en Planes y coberturas -- smoke test que confirma que la seccion renderiza con datos, no valida el detalle completo de cobertura.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP sobre acceder al documento de condicionado en ninguna hoja.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP sobre descargar el condicionado en ninguna hoja.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP sobre el caso de plan sin condicionado disponible en ninguna hoja.</t>
+  </si>
+  <si>
+    <t>Hoja Reintegros, CP-01 (Mobile, unico CP de toda la hoja): muestra la seccion de cuentas de acreditacion -- smoke test de acceso, no ejercita el flujo real de reintegros.</t>
+  </si>
+  <si>
+    <t>Gap real y significativo: la hoja Reintegros de Casos de Prueba.xlsx tiene un solo CP en total (smoke test mobile de acceso). Todo el flujo de solicitud fue probado extensamente pero de forma MANUAL (reintegros-backoffice.ike.qa, ver qa-workspace/decision-log.md IMAS-4101 y relacionados) -- nunca se automatizo como test de Playwright.</t>
+  </si>
+  <si>
+    <t>Mismo gap que la fila anterior -- carga de documentacion probada manualmente, no automatizada.</t>
+  </si>
+  <si>
+    <t>Mismo gap -- validacion de campos del formulario probada manualmente, no automatizada.</t>
+  </si>
+  <si>
+    <t>Mismo gap -- casos de datos invalidos probados manualmente, no automatizados.</t>
+  </si>
+  <si>
+    <t>Mismo gap -- consulta de estado probada manualmente (incluye el hallazgo activo BUG-015, rechazo directo de Calidad), no automatizada.</t>
+  </si>
+  <si>
+    <t>Hoja Miscelaneas, CP-07 (Mobile): abre vetifyplus.com en el navegador del sistema -- automatizado.</t>
+  </si>
+  <si>
+    <t>Hoja Miscelaneas, CP-07 (Mobile): mismo CP que la fila anterior, confirma el acceso -- automatizado.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP sobre contratar un plan adicional desde la WebApp en ninguna hoja.</t>
+  </si>
+  <si>
+    <t>Gap real: no hay CP sobre el caso de plan no elegible para el usuario en ninguna hoja.</t>
+  </si>
+  <si>
+    <t>Gap real de un CP dedicado: no hay una suite de regresion transversal propia en Casos de Prueba.xlsx. Nota: esto se ejercita de forma indirecta cada vez que corre cualquier otro spec (login, navegacion), pero sin una aserción dedicada que lo verifique como su propio caso.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-084</t>
+  </si>
+  <si>
+    <t>14. Control de Acceso</t>
+  </si>
+  <si>
+    <t>Bloqueo de acceso sin ningun plan</t>
+  </si>
+  <si>
+    <t>Validar que un usuario sin plan de Vetify ni de Ike no puede acceder a la WebApp de Ike.</t>
+  </si>
+  <si>
+    <t>Hoja Control de Acceso (IMAS-3742), CP-04: No, sin automatizar. Bloqueado por IMP-005: no hay usuarios de prueba con cuenta en el sistema de identidad de Ike, provisionar no es autoservicio.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-085</t>
+  </si>
+  <si>
+    <t>Acceso exclusivo por tipo de plan</t>
+  </si>
+  <si>
+    <t>Validar que el acceso a la WebApp de Ike depende del tipo de plan: solo Vetify no accede, plan de Ike si accede, ambos planes acceden.</t>
+  </si>
+  <si>
+    <t>Validacion</t>
+  </si>
+  <si>
+    <t>Hoja Control de Acceso, CP-01 (marcado No valida CA01, no prueba lo que dice), CP-02, CP-03, CP-06: los 4 relacionados a esta matriz de acceso estan sin validar de verdad. Mismo bloqueo IMP-005.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-086</t>
+  </si>
+  <si>
+    <t>Regresion: no afecta otros tipos de usuario</t>
+  </si>
+  <si>
+    <t>Validar que el nuevo control de acceso no rompe el login de usuarios que no estan afectados por este cambio.</t>
+  </si>
+  <si>
+    <t>Regresion</t>
+  </si>
+  <si>
+    <t>Hoja Control de Acceso, CP-05: No, sin automatizar. Mismo bloqueo IMP-005.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-087</t>
+  </si>
+  <si>
+    <t>15. Disponibilidad del Sistema</t>
+  </si>
+  <si>
+    <t>Aviso de indisponibilidad general</t>
+  </si>
+  <si>
+    <t>Validar que la pantalla de indisponibilidad aparece cuando el sistema entero cae y se oculta al restablecerse, de forma consistente en todas las pantallas.</t>
+  </si>
+  <si>
+    <t>Hoja Sistema Caido (IMAS-3860), CP-01 y CP-02: 2 de 2 CPs automatizados.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-088</t>
+  </si>
+  <si>
+    <t>Aviso de indisponibilidad de funcionalidad puntual</t>
+  </si>
+  <si>
+    <t>Validar el modal de funcionalidad no disponible (ej. Videollamada caida) y que el resto de la app sigue operativa.</t>
+  </si>
+  <si>
+    <t>Hoja Sistema Caido, CP-03 y CP-04: 2 de 2 CPs automatizados.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-089</t>
+  </si>
+  <si>
+    <t>Canales de contacto (Ayuda)</t>
+  </si>
+  <si>
+    <t>Validar que se muestran los canales de contacto (Emergencias y Atencion al cliente) en la seccion de Ayuda.</t>
+  </si>
+  <si>
+    <t>Hoja Miscelaneas, CP-05 (Mobile): automatizado. Fila agregada porque no tenia equivalente en el roadmap original.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-090</t>
+  </si>
+  <si>
+    <t>Facturas - estado vacio</t>
+  </si>
+  <si>
+    <t>Validar que se muestra el estado vacio correcto cuando el usuario no tiene facturas cargadas.</t>
+  </si>
+  <si>
+    <t>Hoja Miscelaneas, CP-09 (Mobile): automatizado. Fila agregada porque no tenia equivalente en el roadmap original -- es un smoke test de estado vacio, no ejercita el flujo real de reintegro.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-091</t>
+  </si>
+  <si>
+    <t>16. Flujos End-to-End</t>
+  </si>
+  <si>
+    <t>Flujo completo: Creacion de usuario, Compra y Reseteo de contrasena</t>
+  </si>
+  <si>
+    <t>Validar el journey completo del cliente en una sola corrida continua: registrarse, activar la cuenta, comprar un plan y, en otro momento, resetear la contrasena con exito.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-018, QA-AUTO-021, QA-AUTO-001, QA-AUTO-026</t>
+  </si>
+  <si>
+    <t>IMPORTANTE: cada paso por separado SI esta automatizado y pasando (Registracion 100%, Activacion 100%, Compra B2C 50%, Reseteo de contrasena 50%), pero NINGUN test encadena las 4 etapas en una sola corrida continua -- son specs independientes con cuentas distintas. El 0% refleja el journey end-to-end tal como lo pidio la PO, no la cobertura de las partes.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-092</t>
+  </si>
+  <si>
+    <t>Flujo completo: Compra, Carga de credencial y Solicitud de videollamada</t>
+  </si>
+  <si>
+    <t>Validar el journey completo desde que el cliente compra un plan hasta que consigue agendar una videollamada, pasando por cargar la credencial de su mascota, en una sola corrida continua.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-001, QA-AUTO-039, QA-AUTO-048</t>
+  </si>
+  <si>
+    <t>Mismo caso que la fila anterior: las 3 partes estan automatizadas por separado (Compra 50%, Carga de credencial 100%, Solicitar videollamada 100%) pero nunca encadenadas en un solo test end-to-end. Candidato natural a automatizar primero entre los 2 journeys nuevos, porque sus 3 partes ya estan en mejor estado individualmente.</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1110,10 +1428,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1136,7 +1457,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -1239,37 +1560,37 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.60526315789473684</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.42857142857142855</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>6.25E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.17857142857142858</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -1388,7 +1709,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -1464,19 +1785,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>73</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1874,8 +2195,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K87"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -1890,7 +2211,7 @@
     <col min="11" max="11" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1925,7 +2246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -1951,12 +2272,14 @@
         <v>1</v>
       </c>
       <c r="I2" s="4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K2" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -1982,12 +2305,14 @@
         <v>1</v>
       </c>
       <c r="I3" s="4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K3" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -2013,12 +2338,14 @@
         <v>1</v>
       </c>
       <c r="I4" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K4" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
@@ -2044,23 +2371,25 @@
         <v>1</v>
       </c>
       <c r="I5" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K5" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>265</v>
@@ -2078,20 +2407,22 @@
         <v>0</v>
       </c>
       <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K6" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>31</v>
@@ -2109,20 +2440,22 @@
         <v>0</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K7" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -2140,20 +2473,22 @@
         <v>0</v>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K8" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>35</v>
@@ -2171,20 +2506,22 @@
         <v>0</v>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K9" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>37</v>
@@ -2202,20 +2539,22 @@
         <v>0</v>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K10" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>39</v>
@@ -2233,20 +2572,22 @@
         <v>0</v>
       </c>
       <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K11" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>266</v>
@@ -2264,14 +2605,16 @@
         <v>0</v>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K12" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>25</v>
@@ -2295,14 +2638,16 @@
         <v>0</v>
       </c>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K13" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>45</v>
@@ -2326,14 +2671,16 @@
         <v>0</v>
       </c>
       <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K14" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>45</v>
@@ -2357,9 +2704,11 @@
         <v>0</v>
       </c>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K15" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>54</v>
       </c>
@@ -2370,7 +2719,7 @@
         <v>56</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>57</v>
@@ -2385,12 +2734,14 @@
         <v>1</v>
       </c>
       <c r="I16" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K16" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
@@ -2416,12 +2767,14 @@
         <v>1</v>
       </c>
       <c r="I17" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K17" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>62</v>
       </c>
@@ -2447,12 +2800,14 @@
         <v>1</v>
       </c>
       <c r="I18" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K18" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>65</v>
       </c>
@@ -2478,12 +2833,14 @@
         <v>2</v>
       </c>
       <c r="I19" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K19" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>67</v>
       </c>
@@ -2509,12 +2866,14 @@
         <v>2</v>
       </c>
       <c r="I20" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K20" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>70</v>
       </c>
@@ -2540,12 +2899,14 @@
         <v>1</v>
       </c>
       <c r="I21" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K21" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>73</v>
       </c>
@@ -2571,12 +2932,14 @@
         <v>1</v>
       </c>
       <c r="I22" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K22" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>76</v>
       </c>
@@ -2602,12 +2965,14 @@
         <v>2</v>
       </c>
       <c r="I23" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K23" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>79</v>
       </c>
@@ -2633,12 +2998,14 @@
         <v>1</v>
       </c>
       <c r="I24" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K24" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>81</v>
       </c>
@@ -2664,12 +3031,14 @@
         <v>1</v>
       </c>
       <c r="I25" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K25" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>84</v>
       </c>
@@ -2695,12 +3064,14 @@
         <v>1</v>
       </c>
       <c r="I26" s="4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K26" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>87</v>
       </c>
@@ -2726,12 +3097,14 @@
         <v>2</v>
       </c>
       <c r="I27" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K27" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>90</v>
       </c>
@@ -2760,9 +3133,11 @@
         <v>0</v>
       </c>
       <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K28" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>93</v>
       </c>
@@ -2791,9 +3166,11 @@
         <v>0</v>
       </c>
       <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K29" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>96</v>
       </c>
@@ -2822,9 +3199,11 @@
         <v>0</v>
       </c>
       <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K30" s="2" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>99</v>
       </c>
@@ -2853,9 +3232,11 @@
         <v>0</v>
       </c>
       <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K31" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>102</v>
       </c>
@@ -2884,9 +3265,11 @@
         <v>0</v>
       </c>
       <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K32" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>106</v>
       </c>
@@ -2912,12 +3295,14 @@
         <v>2</v>
       </c>
       <c r="I33" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K33" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>110</v>
       </c>
@@ -2943,12 +3328,14 @@
         <v>2</v>
       </c>
       <c r="I34" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K34" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>113</v>
       </c>
@@ -2974,12 +3361,14 @@
         <v>1</v>
       </c>
       <c r="I35" s="4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K35" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>116</v>
       </c>
@@ -3008,9 +3397,11 @@
         <v>0</v>
       </c>
       <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K36" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>119</v>
       </c>
@@ -3039,12 +3430,16 @@
         <v>0</v>
       </c>
       <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
+      <c r="K37" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>300</v>
+      </c>
       <c r="B38" s="2" t="s">
-        <v>276</v>
+        <v>55</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>45</v>
@@ -3061,24 +3456,32 @@
       <c r="G38" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="4"/>
+      <c r="H38" s="2">
+        <v>1</v>
+      </c>
+      <c r="I38" s="4">
+        <v>0</v>
+      </c>
       <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
+      <c r="K38" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>301</v>
+      </c>
       <c r="B39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>52</v>
@@ -3086,12 +3489,18 @@
       <c r="G39" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H39" s="2"/>
-      <c r="I39" s="4"/>
+      <c r="H39" s="2">
+        <v>3</v>
+      </c>
+      <c r="I39" s="4">
+        <v>0</v>
+      </c>
       <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K39" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>122</v>
       </c>
@@ -3117,12 +3526,14 @@
         <v>1</v>
       </c>
       <c r="I40" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K40" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>124</v>
       </c>
@@ -3148,12 +3559,14 @@
         <v>1</v>
       </c>
       <c r="I41" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K41" s="2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
@@ -3179,12 +3592,14 @@
         <v>1</v>
       </c>
       <c r="I42" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K42" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>129</v>
       </c>
@@ -3195,7 +3610,7 @@
         <v>45</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>273</v>
@@ -3210,12 +3625,14 @@
         <v>2</v>
       </c>
       <c r="I43" s="4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K43" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>130</v>
       </c>
@@ -3244,23 +3661,25 @@
         <v>0</v>
       </c>
       <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K44" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>134</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>15</v>
@@ -3272,26 +3691,28 @@
         <v>1</v>
       </c>
       <c r="I45" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K45" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>15</v>
@@ -3303,26 +3724,28 @@
         <v>1</v>
       </c>
       <c r="I46" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K46" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>137</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>15</v>
@@ -3334,24 +3757,28 @@
         <v>2</v>
       </c>
       <c r="I47" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
+      <c r="K47" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>302</v>
+      </c>
       <c r="B48" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>15</v>
@@ -3359,12 +3786,18 @@
       <c r="G48" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H48" s="2"/>
-      <c r="I48" s="4"/>
+      <c r="H48" s="2">
+        <v>1</v>
+      </c>
+      <c r="I48" s="4">
+        <v>100</v>
+      </c>
       <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K48" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>138</v>
       </c>
@@ -3390,12 +3823,14 @@
         <v>1</v>
       </c>
       <c r="I49" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K49" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>142</v>
       </c>
@@ -3424,9 +3859,11 @@
         <v>0</v>
       </c>
       <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K50" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>145</v>
       </c>
@@ -3455,9 +3892,11 @@
         <v>0</v>
       </c>
       <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K51" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>148</v>
       </c>
@@ -3483,12 +3922,14 @@
         <v>1</v>
       </c>
       <c r="I52" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K52" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>151</v>
       </c>
@@ -3517,9 +3958,11 @@
         <v>0</v>
       </c>
       <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K53" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>154</v>
       </c>
@@ -3548,21 +3991,25 @@
         <v>0</v>
       </c>
       <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="2"/>
+      <c r="K54" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>303</v>
+      </c>
       <c r="B55" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>15</v>
@@ -3570,12 +4017,18 @@
       <c r="G55" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H55" s="2"/>
-      <c r="I55" s="4"/>
+      <c r="H55" s="2">
+        <v>1</v>
+      </c>
+      <c r="I55" s="4">
+        <v>100</v>
+      </c>
       <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K55" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>157</v>
       </c>
@@ -3604,9 +4057,11 @@
         <v>0</v>
       </c>
       <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K56" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>161</v>
       </c>
@@ -3635,9 +4090,11 @@
         <v>0</v>
       </c>
       <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K57" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>164</v>
       </c>
@@ -3666,9 +4123,11 @@
         <v>0</v>
       </c>
       <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K58" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>167</v>
       </c>
@@ -3697,9 +4156,11 @@
         <v>0</v>
       </c>
       <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K59" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>170</v>
       </c>
@@ -3728,9 +4189,11 @@
         <v>0</v>
       </c>
       <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K60" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>173</v>
       </c>
@@ -3756,12 +4219,14 @@
         <v>1</v>
       </c>
       <c r="I61" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K61" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>177</v>
       </c>
@@ -3790,9 +4255,11 @@
         <v>0</v>
       </c>
       <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K62" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>180</v>
       </c>
@@ -3821,9 +4288,11 @@
         <v>0</v>
       </c>
       <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K63" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>183</v>
       </c>
@@ -3852,9 +4321,11 @@
         <v>0</v>
       </c>
       <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K64" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>186</v>
       </c>
@@ -3880,12 +4351,14 @@
         <v>1</v>
       </c>
       <c r="I65" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K65" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>190</v>
       </c>
@@ -3914,9 +4387,11 @@
         <v>0</v>
       </c>
       <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K66" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>193</v>
       </c>
@@ -3945,9 +4420,11 @@
         <v>0</v>
       </c>
       <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K67" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>196</v>
       </c>
@@ -3976,9 +4453,11 @@
         <v>0</v>
       </c>
       <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K68" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>199</v>
       </c>
@@ -4007,9 +4486,11 @@
         <v>0</v>
       </c>
       <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K69" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>202</v>
       </c>
@@ -4038,17 +4519,19 @@
         <v>0</v>
       </c>
       <c r="J70" s="2"/>
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K70" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>207</v>
@@ -4066,20 +4549,22 @@
         <v>2</v>
       </c>
       <c r="I71" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J71" s="2"/>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K71" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>209</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>210</v>
@@ -4097,20 +4582,22 @@
         <v>2</v>
       </c>
       <c r="I72" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J72" s="2"/>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K72" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>213</v>
@@ -4131,17 +4618,19 @@
         <v>0</v>
       </c>
       <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K73" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>215</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>216</v>
@@ -4162,9 +4651,11 @@
         <v>0</v>
       </c>
       <c r="J74" s="2"/>
-      <c r="K74" s="2"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K74" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>219</v>
       </c>
@@ -4193,9 +4684,11 @@
         <v>0</v>
       </c>
       <c r="J75" s="2"/>
-      <c r="K75" s="2"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K75" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>223</v>
       </c>
@@ -4224,9 +4717,11 @@
         <v>0</v>
       </c>
       <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K76" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>226</v>
       </c>
@@ -4255,9 +4750,11 @@
         <v>0</v>
       </c>
       <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-    </row>
-    <row r="78" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K77" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>229</v>
       </c>
@@ -4286,7 +4783,303 @@
         <v>0</v>
       </c>
       <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
+      <c r="K78" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>365</v>
+      </c>
+      <c r="B79" t="s">
+        <v>366</v>
+      </c>
+      <c r="C79" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" t="s">
+        <v>367</v>
+      </c>
+      <c r="E79" t="s">
+        <v>368</v>
+      </c>
+      <c r="F79" t="s">
+        <v>52</v>
+      </c>
+      <c r="G79" t="s">
+        <v>16</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="K79" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>370</v>
+      </c>
+      <c r="B80" t="s">
+        <v>366</v>
+      </c>
+      <c r="C80" t="s">
+        <v>45</v>
+      </c>
+      <c r="D80" t="s">
+        <v>371</v>
+      </c>
+      <c r="E80" t="s">
+        <v>372</v>
+      </c>
+      <c r="F80" t="s">
+        <v>373</v>
+      </c>
+      <c r="G80" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="K80" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>375</v>
+      </c>
+      <c r="B81" t="s">
+        <v>366</v>
+      </c>
+      <c r="C81" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" t="s">
+        <v>376</v>
+      </c>
+      <c r="E81" t="s">
+        <v>377</v>
+      </c>
+      <c r="F81" t="s">
+        <v>378</v>
+      </c>
+      <c r="G81" t="s">
+        <v>53</v>
+      </c>
+      <c r="H81">
+        <v>2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="K81" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>380</v>
+      </c>
+      <c r="B82" t="s">
+        <v>381</v>
+      </c>
+      <c r="C82" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" t="s">
+        <v>382</v>
+      </c>
+      <c r="E82" t="s">
+        <v>383</v>
+      </c>
+      <c r="F82" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82">
+        <v>1</v>
+      </c>
+      <c r="I82">
+        <v>100</v>
+      </c>
+      <c r="K82" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>385</v>
+      </c>
+      <c r="B83" t="s">
+        <v>381</v>
+      </c>
+      <c r="C83" t="s">
+        <v>45</v>
+      </c>
+      <c r="D83" t="s">
+        <v>386</v>
+      </c>
+      <c r="E83" t="s">
+        <v>387</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83">
+        <v>100</v>
+      </c>
+      <c r="K83" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>389</v>
+      </c>
+      <c r="B84" t="s">
+        <v>135</v>
+      </c>
+      <c r="C84" t="s">
+        <v>45</v>
+      </c>
+      <c r="D84" t="s">
+        <v>390</v>
+      </c>
+      <c r="E84" t="s">
+        <v>391</v>
+      </c>
+      <c r="F84" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" t="s">
+        <v>53</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
+      </c>
+      <c r="I84">
+        <v>100</v>
+      </c>
+      <c r="K84" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>393</v>
+      </c>
+      <c r="B85" t="s">
+        <v>187</v>
+      </c>
+      <c r="C85" t="s">
+        <v>45</v>
+      </c>
+      <c r="D85" t="s">
+        <v>394</v>
+      </c>
+      <c r="E85" t="s">
+        <v>395</v>
+      </c>
+      <c r="F85" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s">
+        <v>133</v>
+      </c>
+      <c r="H85">
+        <v>3</v>
+      </c>
+      <c r="I85">
+        <v>100</v>
+      </c>
+      <c r="K85" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>397</v>
+      </c>
+      <c r="B86" t="s">
+        <v>398</v>
+      </c>
+      <c r="C86" t="s">
+        <v>45</v>
+      </c>
+      <c r="D86" t="s">
+        <v>399</v>
+      </c>
+      <c r="E86" t="s">
+        <v>400</v>
+      </c>
+      <c r="F86" t="s">
+        <v>378</v>
+      </c>
+      <c r="G86" t="s">
+        <v>16</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86" t="s">
+        <v>401</v>
+      </c>
+      <c r="K86" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>403</v>
+      </c>
+      <c r="B87" t="s">
+        <v>398</v>
+      </c>
+      <c r="C87" t="s">
+        <v>45</v>
+      </c>
+      <c r="D87" t="s">
+        <v>404</v>
+      </c>
+      <c r="E87" t="s">
+        <v>405</v>
+      </c>
+      <c r="F87" t="s">
+        <v>378</v>
+      </c>
+      <c r="G87" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87" t="s">
+        <v>406</v>
+      </c>
+      <c r="K87" t="s">
+        <v>407</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K78" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -4321,18 +5114,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="7" width="3" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="7" width="3" customWidth="1"/>
     <col min="8" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="7"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -4344,7 +5138,7 @@
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
       <c r="B2" s="15" t="s">
         <v>232</v>
@@ -4358,7 +5152,7 @@
       <c r="I2" s="16"/>
       <c r="J2" s="16"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -4370,7 +5164,7 @@
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -4382,7 +5176,7 @@
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" ht="21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="21" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="8" t="s">
         <v>233</v>
@@ -4396,7 +5190,7 @@
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
@@ -4408,7 +5202,7 @@
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="17" t="s">
         <v>234</v>
@@ -4426,28 +5220,28 @@
       <c r="I7" s="18"/>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="20">
         <f>COUNTA('Roadmap QA Automation'!A2:A1998)</f>
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="19">
+      <c r="E8" s="21">
         <f>IFERROR(AVERAGE('Roadmap QA Automation'!I2:I1998)/100,0)</f>
-        <v>0</v>
+        <v>0.38953488372093026</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="7"/>
       <c r="H8" s="19">
         <f>COUNTIF('Roadmap QA Automation'!I2:I1998,100)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -4459,7 +5253,7 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -4471,7 +5265,7 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -4483,7 +5277,7 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
       <c r="B12" s="9" t="s">
         <v>237</v>
@@ -4497,7 +5291,7 @@
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="10" t="s">
         <v>1</v>
@@ -4515,18 +5309,18 @@
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B14)</f>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B14,3)&amp;"*")</f>
         <v>4</v>
       </c>
       <c r="D14" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B14,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B14,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>0.75</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -4535,17 +5329,17 @@
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
       <c r="B15" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B15)</f>
-        <v>0</v>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B15,3)&amp;"*")</f>
+        <v>10</v>
       </c>
       <c r="D15" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B15,'Roadmap QA Automation'!I:I)/100,0)</f>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B15,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
         <v>0</v>
       </c>
       <c r="E15" s="7"/>
@@ -4555,18 +5349,18 @@
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7"/>
       <c r="B16" s="7" t="s">
         <v>55</v>
       </c>
       <c r="C16" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B16)</f>
-        <v>17</v>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B16,3)&amp;"*")</f>
+        <v>19</v>
       </c>
       <c r="D16" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B16,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B16,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>0.60526315789473684</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -4575,18 +5369,18 @@
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
         <v>107</v>
       </c>
       <c r="C17" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B17)</f>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B17,3)&amp;"*")</f>
         <v>5</v>
       </c>
       <c r="D17" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B17,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B17,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>0.4</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -4595,18 +5389,18 @@
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
       <c r="B18" s="7" t="s">
         <v>123</v>
       </c>
       <c r="C18" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B18)</f>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B18,3)&amp;"*")</f>
         <v>5</v>
       </c>
       <c r="D18" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B18,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B18,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>0.7</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -4615,18 +5409,18 @@
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="7" t="s">
         <v>135</v>
       </c>
       <c r="C19" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B19)</f>
-        <v>0</v>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B19,3)&amp;"*")</f>
+        <v>5</v>
       </c>
       <c r="D19" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B19,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B19,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>1</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -4635,18 +5429,18 @@
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
       <c r="B20" s="7" t="s">
         <v>139</v>
       </c>
       <c r="C20" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B20)</f>
-        <v>6</v>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B20,3)&amp;"*")</f>
+        <v>7</v>
       </c>
       <c r="D20" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B20,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B20,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -4655,17 +5449,17 @@
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
         <v>158</v>
       </c>
       <c r="C21" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B21)</f>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B21,3)&amp;"*")</f>
         <v>5</v>
       </c>
       <c r="D21" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B21,'Roadmap QA Automation'!I:I)/100,0)</f>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B21,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
         <v>0</v>
       </c>
       <c r="E21" s="7"/>
@@ -4675,18 +5469,18 @@
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7" t="s">
         <v>174</v>
       </c>
       <c r="C22" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B22)</f>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B22,3)&amp;"*")</f>
         <v>4</v>
       </c>
       <c r="D22" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B22,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B22,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>6.25E-2</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -4695,18 +5489,18 @@
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
       <c r="B23" s="7" t="s">
         <v>187</v>
       </c>
       <c r="C23" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B23)</f>
-        <v>6</v>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B23,3)&amp;"*")</f>
+        <v>7</v>
       </c>
       <c r="D23" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B23,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B23,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>0.17857142857142858</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -4715,18 +5509,18 @@
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7"/>
       <c r="B24" s="7" t="s">
         <v>206</v>
       </c>
       <c r="C24" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B24)</f>
-        <v>0</v>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B24,3)&amp;"*")</f>
+        <v>4</v>
       </c>
       <c r="D24" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B24,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B24,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>0.5</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -4735,17 +5529,17 @@
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="7"/>
       <c r="B25" s="7" t="s">
         <v>218</v>
       </c>
       <c r="C25" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B25)</f>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B25,3)&amp;"*")</f>
         <v>0</v>
       </c>
       <c r="D25" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B25,'Roadmap QA Automation'!I:I)/100,0)</f>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B25,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
         <v>0</v>
       </c>
       <c r="E25" s="7"/>
@@ -4755,17 +5549,17 @@
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
       <c r="B26" s="7" t="s">
         <v>220</v>
       </c>
       <c r="C26" s="7">
-        <f>COUNTIF('Roadmap QA Automation'!B:B,B26)</f>
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B26,3)&amp;"*")</f>
         <v>4</v>
       </c>
       <c r="D26" s="11">
-        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,B26,'Roadmap QA Automation'!I:I)/100,0)</f>
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B26,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
         <v>0</v>
       </c>
       <c r="E26" s="7"/>
@@ -4775,11 +5569,19 @@
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
+      <c r="B27" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C27" s="7">
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B27,3)&amp;"*")</f>
+        <v>3</v>
+      </c>
+      <c r="D27" s="11">
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B27,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>0</v>
+      </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -4787,11 +5589,19 @@
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="B28" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C28" s="7">
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B28,3)&amp;"*")</f>
+        <v>2</v>
+      </c>
+      <c r="D28" s="11">
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B28,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>1</v>
+      </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -4799,11 +5609,19 @@
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+      <c r="B29" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C29" s="7">
+        <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B29,3)&amp;"*")</f>
+        <v>2</v>
+      </c>
+      <c r="D29" s="11">
+        <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B29,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
+        <v>0</v>
+      </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -4811,7 +5629,7 @@
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A30" s="7"/>
       <c r="B30" s="9" t="s">
         <v>240</v>
@@ -4825,7 +5643,7 @@
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="7"/>
       <c r="B31" s="10" t="s">
         <v>241</v>
@@ -4841,14 +5659,14 @@
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="7"/>
       <c r="B32" s="7" t="s">
         <v>243</v>
       </c>
       <c r="C32" s="7">
         <f>COUNTIF('Roadmap QA Automation'!I:I,0)</f>
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -4858,14 +5676,14 @@
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="7"/>
       <c r="B33" s="7" t="s">
         <v>244</v>
       </c>
       <c r="C33" s="7">
         <f>COUNTIF('Roadmap QA Automation'!I:I,25)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -4875,14 +5693,14 @@
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="7"/>
       <c r="B34" s="7" t="s">
         <v>245</v>
       </c>
       <c r="C34" s="7">
         <f>COUNTIF('Roadmap QA Automation'!I:I,50)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -4892,14 +5710,14 @@
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="7"/>
       <c r="B35" s="7" t="s">
         <v>246</v>
       </c>
       <c r="C35" s="7">
         <f>COUNTIF('Roadmap QA Automation'!I:I,75)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -4909,14 +5727,14 @@
       <c r="I35" s="7"/>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="7"/>
       <c r="B36" s="7" t="s">
         <v>247</v>
       </c>
       <c r="C36" s="7">
         <f>COUNTIF('Roadmap QA Automation'!I:I,100)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -4926,7 +5744,7 @@
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7"/>
@@ -4938,7 +5756,7 @@
       <c r="I37" s="7"/>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
@@ -4950,7 +5768,7 @@
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="7"/>
@@ -4962,7 +5780,7 @@
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" ht="36" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A40" s="7"/>
       <c r="B40" s="9" t="s">
         <v>248</v>
@@ -4976,7 +5794,7 @@
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="7"/>
       <c r="B41" s="10" t="s">
         <v>6</v>
@@ -4994,18 +5812,18 @@
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="7"/>
       <c r="B42" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="7">
         <f>COUNTIF('Roadmap QA Automation'!G:G,B42)</f>
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D42" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!G:G,B42,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>0.37698412698412698</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
@@ -5014,18 +5832,18 @@
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="7"/>
       <c r="B43" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C43" s="7">
         <f>COUNTIF('Roadmap QA Automation'!G:G,B43)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D43" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!G:G,B43,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>0.46052631578947367</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
@@ -5034,18 +5852,18 @@
       <c r="I43" s="7"/>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="7"/>
       <c r="B44" s="7" t="s">
         <v>133</v>
       </c>
       <c r="C44" s="7">
         <f>COUNTIF('Roadmap QA Automation'!G:G,B44)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D44" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!G:G,B44,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -5054,7 +5872,7 @@
       <c r="I44" s="7"/>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -5066,7 +5884,7 @@
       <c r="I45" s="7"/>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="7"/>
       <c r="B46" s="7"/>
       <c r="C46" s="7"/>
@@ -5078,7 +5896,7 @@
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="1:10" ht="18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A47" s="7"/>
       <c r="B47" s="9" t="s">
         <v>249</v>
@@ -5092,7 +5910,7 @@
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="7"/>
       <c r="B48" s="10" t="s">
         <v>2</v>
@@ -5110,7 +5928,7 @@
       <c r="I48" s="7"/>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="7"/>
       <c r="B49" s="7" t="s">
         <v>13</v>
@@ -5121,7 +5939,7 @@
       </c>
       <c r="D49" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!C:C,B49,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
@@ -5130,7 +5948,7 @@
       <c r="I49" s="7"/>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="7"/>
       <c r="B50" s="7" t="s">
         <v>18</v>
@@ -5141,7 +5959,7 @@
       </c>
       <c r="D50" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!C:C,B50,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>0.16666666666666669</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
@@ -5150,7 +5968,7 @@
       <c r="I50" s="7"/>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="7"/>
       <c r="B51" s="7" t="s">
         <v>21</v>
@@ -5161,7 +5979,7 @@
       </c>
       <c r="D51" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!C:C,B51,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
@@ -5170,7 +5988,7 @@
       <c r="I51" s="7"/>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="7"/>
       <c r="B52" s="7" t="s">
         <v>25</v>
@@ -5181,7 +5999,7 @@
       </c>
       <c r="D52" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!C:C,B52,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>0.33333333333333337</v>
       </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
@@ -5190,18 +6008,18 @@
       <c r="I52" s="7"/>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="7"/>
       <c r="B53" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C53" s="7">
         <f>COUNTIF('Roadmap QA Automation'!C:C,B53)</f>
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D53" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!C:C,B53,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>0.38970588235294118</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
@@ -5228,18 +6046,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:C18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:3" ht="26.25" x14ac:dyDescent="0.4">
       <c r="B2" s="12" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" ht="30" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
         <v>251</v>
       </c>
@@ -5247,17 +6065,17 @@
         <v>252</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="14"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="13" t="s">
         <v>253</v>
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>243</v>
       </c>
@@ -5265,7 +6083,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
         <v>244</v>
       </c>
@@ -5273,7 +6091,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="14" t="s">
         <v>245</v>
       </c>
@@ -5281,7 +6099,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>246</v>
       </c>
@@ -5289,7 +6107,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="14" t="s">
         <v>247</v>
       </c>
@@ -5297,17 +6115,17 @@
         <v>258</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="14"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="14" t="s">
         <v>16</v>
       </c>
@@ -5315,7 +6133,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
         <v>53</v>
       </c>
@@ -5323,7 +6141,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>133</v>
       </c>
@@ -5331,11 +6149,11 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="14"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="13" t="s">
         <v>262</v>
       </c>
@@ -5564,13 +6382,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A512D99-C2FC-42B8-8FDB-89CED4284B88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A512D99-C2FC-42B8-8FDB-89CED4284B88}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e"/>
+    <ds:schemaRef ds:uri="823bb257-b027-4d06-8b2f-053335b328b1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{211C9EF2-99F3-47CC-A9EA-437B32406790}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{211C9EF2-99F3-47CC-A9EA-437B32406790}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{347876AB-BDAE-4A3D-A9BF-1638E774D861}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{347876AB-BDAE-4A3D-A9BF-1638E774D861}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e"/>
+    <ds:schemaRef ds:uri="823bb257-b027-4d06-8b2f-053335b328b1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/documentation/Automation Vetify.xlsx
+++ b/documentation/Automation Vetify.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\ike\vetify-automation\automation\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929DFDDE-F32E-4095-8CAA-1179C3EEE175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41B8FEA-BD83-4820-998D-D9F3C411D1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="416">
   <si>
     <t>ID</t>
   </si>
@@ -1263,6 +1263,30 @@
   </si>
   <si>
     <t>Mismo caso que la fila anterior: las 3 partes estan automatizadas por separado (Compra 50%, Carga de credencial 100%, Solicitar videollamada 100%) pero nunca encadenadas en un solo test end-to-end. Candidato natural a automatizar primero entre los 2 journeys nuevos, porque sus 3 partes ya estan en mejor estado individualmente.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-093</t>
+  </si>
+  <si>
+    <t>Banner Cooper en Home</t>
+  </si>
+  <si>
+    <t>Validar que el banner de Cooper se muestra en Home para los 3 segmentos (Vetify B2C, OSDE Capitado, OSDE Adquirente).</t>
+  </si>
+  <si>
+    <t>IMAS-4356/IMAS-4435. tests/projects/vetify-webapp/navigation.spec.ts TS-05, 3 casos, verificado Desktop y Mobile (Android).</t>
+  </si>
+  <si>
+    <t>QA-AUTO-094</t>
+  </si>
+  <si>
+    <t>Menu Beneficios - segmentacion Cooper/Vetify PLUS</t>
+  </si>
+  <si>
+    <t>Validar que el menu lateral (seccion Beneficios) muestra Cooper y Vetify PLUS para B2C, y solo Cooper para OSDE Capitado.</t>
+  </si>
+  <si>
+    <t>IMAS-4356/IMAS-4435. TS-04 TC-01/02/03, verificado Desktop y Mobile. OSDE Adquirente no automatizado a proposito: la segmentacion real depende del policyId (producto real) de la cuenta, no del segmento -- ver docs/conocimiento-sistema.md.</t>
   </si>
 </sst>
 </file>
@@ -1590,7 +1614,7 @@
                   <c:v>0.17857142857142858</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.5</c:v>
+                  <c:v>0.66666666666666674</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -1797,7 +1821,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2195,7 +2219,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -5079,6 +5103,70 @@
       </c>
       <c r="K87" t="s">
         <v>407</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>408</v>
+      </c>
+      <c r="B88" t="s">
+        <v>280</v>
+      </c>
+      <c r="C88" t="s">
+        <v>45</v>
+      </c>
+      <c r="D88" t="s">
+        <v>409</v>
+      </c>
+      <c r="E88" t="s">
+        <v>410</v>
+      </c>
+      <c r="F88" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" t="s">
+        <v>16</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="I88">
+        <v>100</v>
+      </c>
+      <c r="K88" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>412</v>
+      </c>
+      <c r="B89" t="s">
+        <v>280</v>
+      </c>
+      <c r="C89" t="s">
+        <v>45</v>
+      </c>
+      <c r="D89" t="s">
+        <v>413</v>
+      </c>
+      <c r="E89" t="s">
+        <v>414</v>
+      </c>
+      <c r="F89" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89">
+        <v>100</v>
+      </c>
+      <c r="K89" t="s">
+        <v>415</v>
       </c>
     </row>
   </sheetData>
@@ -5224,19 +5312,19 @@
       <c r="A8" s="7"/>
       <c r="B8" s="20">
         <f>COUNTA('Roadmap QA Automation'!A2:A1998)</f>
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="7"/>
       <c r="E8" s="21">
         <f>IFERROR(AVERAGE('Roadmap QA Automation'!I2:I1998)/100,0)</f>
-        <v>0.38953488372093026</v>
+        <v>0.40340909090909094</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="7"/>
       <c r="H8" s="19">
         <f>COUNTIF('Roadmap QA Automation'!I2:I1998,100)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="7"/>
@@ -5516,11 +5604,11 @@
       </c>
       <c r="C24" s="7">
         <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B24,3)&amp;"*")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B24,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.5</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -5734,7 +5822,7 @@
       </c>
       <c r="C36" s="7">
         <f>COUNTIF('Roadmap QA Automation'!I:I,100)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -5819,11 +5907,11 @@
       </c>
       <c r="C42" s="7">
         <f>COUNTIF('Roadmap QA Automation'!G:G,B42)</f>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D42" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!G:G,B42,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.37698412698412698</v>
+        <v>0.39615384615384613</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
@@ -6015,11 +6103,11 @@
       </c>
       <c r="C53" s="7">
         <f>COUNTIF('Roadmap QA Automation'!C:C,B53)</f>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D53" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!C:C,B53,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.38970588235294118</v>
+        <v>0.40714285714285714</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
@@ -6167,6 +6255,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="823bb257-b027-4d06-8b2f-053335b328b1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009F842B2145328244B4B47741AC555AE2" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="783508ae003506b91aa2be35b4ebc887">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e" xmlns:ns3="823bb257-b027-4d06-8b2f-053335b328b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b965eb5b8ebcdb894d7355c785d1653" ns2:_="" ns3:_="">
     <xsd:import namespace="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e"/>
@@ -6361,27 +6469,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{347876AB-BDAE-4A3D-A9BF-1638E774D861}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e"/>
+    <ds:schemaRef ds:uri="823bb257-b027-4d06-8b2f-053335b328b1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="823bb257-b027-4d06-8b2f-053335b328b1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{211C9EF2-99F3-47CC-A9EA-437B32406790}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A512D99-C2FC-42B8-8FDB-89CED4284B88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6398,23 +6505,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{211C9EF2-99F3-47CC-A9EA-437B32406790}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{347876AB-BDAE-4A3D-A9BF-1638E774D861}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e"/>
-    <ds:schemaRef ds:uri="823bb257-b027-4d06-8b2f-053335b328b1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/documentation/Automation Vetify.xlsx
+++ b/documentation/Automation Vetify.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41B8FEA-BD83-4820-998D-D9F3C411D1C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64C5346-3ABC-4244-A1BD-17512FAEABDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roadmap QA Automation" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="427">
   <si>
     <t>ID</t>
   </si>
@@ -953,12 +953,6 @@
     <t>QA-AUTO-083</t>
   </si>
   <si>
-    <t>Incluye TS-01 a TS-07 de Flujo de Compra (compra exitosa, fallida, asociacion con usuario existente, cupones, formulario pasos 1-3). 19/31 CPs automatizados. Principal freno: TS-04 Cupones (1/7) por falta de un cupon de prueba real en el ambiente de QA -- es un tema de datos/negocio, no de codigo.</t>
-  </si>
-  <si>
-    <t>Incluye TS-01 a TS-07. 16/31 CPs automatizados. Mismo freno de cupon que B2C (TS-04, 1/7). Pendiente de confirmar: TS-01 (compra exitosa) figura 0/8 en Casos de Prueba.xlsx, pero hoy (29/08) hay un test real de compra exitosa para OSDE Adquirente que corre y pasa -- posible desactualizacion del tracker tactico, no de este roadmap.</t>
-  </si>
-  <si>
     <t>5/5 CPs automatizados (TS-01 Proceso de Compra + TS-02 Validacion de formulario).</t>
   </si>
   <si>
@@ -980,9 +974,6 @@
     <t>TS-01 Registracion CP-02 (Contrasena debil) + CP-05 (Campos obligatorios) -- automatizados en los 4 productos.</t>
   </si>
   <si>
-    <t>TS-03 Activacion de Cuenta completo: 5/5 CPs automatizados (campos obligatorios, tipos de documento, documento no existente/ya registrado, activacion exitosa).</t>
-  </si>
-  <si>
     <t>Cubierto implicitamente por TS-01 CP-04 (Registracion exitosa, incluye setear contrasena valida). No hay un CP dedicado solo a crear contrasena, pero el camino feliz esta probado.</t>
   </si>
   <si>
@@ -995,45 +986,15 @@
     <t>TS-02 Iniciar Sesion CP-01 (Contrasena incorrecta) + CP-02 (Email no existente) -- automatizados.</t>
   </si>
   <si>
-    <t>Incluye 2 sub-flujos con estados distintos: solicitar el reset (TS-04 IMAS-3215, 5/5 automatizado) funciona; completar el cambio via el link (TS-05 Cambio de Contrasena, 0/5) esta bloqueado por el problema de rate-limit/invalidacion de ticket documentado 2026-08-29. 5/10 CPs combinados.</t>
-  </si>
-  <si>
     <t>TS-04 Olvide contrasena CP-03 (Negativo, email no registrado) -- automatizado.</t>
   </si>
   <si>
-    <t>Gap real: no existe un CP dedicado a cambiar contrasena desde un usuario ya autenticado (distinto del reseteo via email) en ninguna hoja de Casos de Prueba.xlsx revisada hasta ahora (Flujo de Compra, Gestion de Usuario, Perfil).</t>
-  </si>
-  <si>
-    <t>Mismo gap que la fila anterior -- no hay CP de cambio de contrasena logueado, por lo tanto tampoco de su variante de rechazo.</t>
-  </si>
-  <si>
-    <t>Gap real: no hay un CP dedicado a Logout en ninguna hoja revisada. Nota aparte: existe un bug conocido de logout en Prestadores (BUG-008, Auth0 no cierra sesion) pero es un hallazgo puntual, no una suite de casos de Logout general.</t>
-  </si>
-  <si>
-    <t>Gap real: no hay CP de acceso a contenido protegido tras logout en las hojas revisadas.</t>
-  </si>
-  <si>
-    <t>Gap real: no hay CP de persistencia de sesion ante refresh en las hojas revisadas.</t>
-  </si>
-  <si>
-    <t>Gap real: no hay ningun CP de Tour de onboarding en Casos de Prueba.xlsx todavia -- funcionalidad nunca disenada como caso de prueba.</t>
-  </si>
-  <si>
-    <t>Mismo gap que la fila anterior.</t>
-  </si>
-  <si>
     <t>Hoja Perfil, CP Visualizacion del perfil -- automatizado (desktop y mobile).</t>
   </si>
   <si>
     <t>Hoja Perfil: cambiar foto (automatizado) y actualizar telefono (automatizado) SI estan cubiertos. Cambiar DNI es el punto debil: 2 de 4 CPs ni siquiera estan escritos todavia (marcados DBD en el Excel tactico) y los otros 2 estan escritos pero no automatizados. 2/6 CPs reales automatizados.</t>
   </si>
   <si>
-    <t>Gap real: no hay CP dedicado a ver el detalle completo de una mascota (datos, plan, servicios asociados) en ninguna hoja revisada.</t>
-  </si>
-  <si>
-    <t>Gap real: no hay CP dedicado a cambiar la mascota activa/contexto. Existe un selector de mascota en otras pantallas (ej. videollamada) pero sin CP propio de este comportamiento.</t>
-  </si>
-  <si>
     <t>Hoja Credenciales, TS-01 Visualizacion de Planes (4/4) + TS-04 Ver Credenciales (2/2) -- 6/6 CPs automatizados.</t>
   </si>
   <si>
@@ -1088,21 +1049,9 @@
     <t>Hoja Miscelaneas, CP-06 (Mobile): muestra la historia clinica de una mascota -- automatizado.</t>
   </si>
   <si>
-    <t>Gap real: no hay ningun CP sobre el mapa de prestadores o veterinarias en ninguna hoja de Casos de Prueba.xlsx (incluyendo Miscelaneas, que no lo menciona).</t>
-  </si>
-  <si>
     <t>Hoja Miscelaneas, CP-02 (Mobile): ve al menos un plan en Planes y coberturas -- smoke test que confirma que la seccion renderiza con datos, no valida el detalle completo de cobertura.</t>
   </si>
   <si>
-    <t>Gap real: no hay CP sobre acceder al documento de condicionado en ninguna hoja.</t>
-  </si>
-  <si>
-    <t>Gap real: no hay CP sobre descargar el condicionado en ninguna hoja.</t>
-  </si>
-  <si>
-    <t>Gap real: no hay CP sobre el caso de plan sin condicionado disponible en ninguna hoja.</t>
-  </si>
-  <si>
     <t>Hoja Reintegros, CP-01 (Mobile, unico CP de toda la hoja): muestra la seccion de cuentas de acreditacion -- smoke test de acceso, no ejercita el flujo real de reintegros.</t>
   </si>
   <si>
@@ -1127,15 +1076,6 @@
     <t>Hoja Miscelaneas, CP-07 (Mobile): mismo CP que la fila anterior, confirma el acceso -- automatizado.</t>
   </si>
   <si>
-    <t>Gap real: no hay CP sobre contratar un plan adicional desde la WebApp en ninguna hoja.</t>
-  </si>
-  <si>
-    <t>Gap real: no hay CP sobre el caso de plan no elegible para el usuario en ninguna hoja.</t>
-  </si>
-  <si>
-    <t>Gap real de un CP dedicado: no hay una suite de regresion transversal propia en Casos de Prueba.xlsx. Nota: esto se ejercita de forma indirecta cada vez que corre cualquier otro spec (login, navegacion), pero sin una aserción dedicada que lo verifique como su propio caso.</t>
-  </si>
-  <si>
     <t>QA-AUTO-084</t>
   </si>
   <si>
@@ -1247,9 +1187,6 @@
     <t>QA-AUTO-018, QA-AUTO-021, QA-AUTO-001, QA-AUTO-026</t>
   </si>
   <si>
-    <t>IMPORTANTE: cada paso por separado SI esta automatizado y pasando (Registracion 100%, Activacion 100%, Compra B2C 50%, Reseteo de contrasena 50%), pero NINGUN test encadena las 4 etapas en una sola corrida continua -- son specs independientes con cuentas distintas. El 0% refleja el journey end-to-end tal como lo pidio la PO, no la cobertura de las partes.</t>
-  </si>
-  <si>
     <t>QA-AUTO-092</t>
   </si>
   <si>
@@ -1287,6 +1224,102 @@
   </si>
   <si>
     <t>IMAS-4356/IMAS-4435. TS-04 TC-01/02/03, verificado Desktop y Mobile. OSDE Adquirente no automatizado a proposito: la segmentacion real depende del policyId (producto real) de la cuenta, no del segmento -- ver docs/conocimiento-sistema.md.</t>
+  </si>
+  <si>
+    <t>Incluye TS-01 a TS-07 de Flujo de Compra (compra exitosa, fallida, asociacion con usuario existente, cupones, formulario pasos 1-3). 19/31 CPs automatizados. Principal freno: TS-04 Cupones (1/7) por falta de un cupon de prueba real en el ambiente de QA -- es un tema de datos/negocio, no de codigo. Re-auditoria 2026-09-06: se corrio toda la suite de compra de nuevo -- 7 de 20 casos fallaron, pero las 7 fallas son comportamiento erratico del sandbox de MercadoPago (tarjetas 'aprobadas' que rechaza, una 'rechazada' que aprueba, motivo de rechazo equivocado), no bugs de test ni del producto. Documentado en BUG-035. El numero de CPs automatizados (19/31) no cambia -- es un problema de estabilidad del ambiente de pruebas de pago, no un gap de automatizacion.</t>
+  </si>
+  <si>
+    <t>Incluye TS-01 a TS-07. 16/31 CPs automatizados. Mismo freno de cupon que B2C (TS-04, 1/7). Pendiente de confirmar: TS-01 (compra exitosa) figura 0/8 en Casos de Prueba.xlsx, pero hoy (29/08) hay un test real de compra exitosa para OSDE Adquirente que corre y pasa -- posible desactualizacion del tracker tactico, no de este roadmap. Actualizacion 2026-09-06: se confirmaron 3 intentos reales de compra consecutivos, todos con error de servidor (no el rechazo antifraude mas leve visto antes) -- documentado como BUG-034, nuevo y persistente, bloquea ademas la verificacion de TS-05 IMAS-3218 (ver fila de Recuperacion de contrasena). No es un problema de automatizacion, es del ambiente de QA.</t>
+  </si>
+  <si>
+    <t>TS-03 Activacion de Cuenta completo: 5/5 CPs automatizados (campos obligatorios, tipos de documento, documento no existente/ya registrado, activacion exitosa). Nota 2026-09-06: se confirmo y arreglo una causa raiz real que hacia fallar la activacion de cuentas 'nunca antes vistas' (el sistema devolvia 'la cuenta ya existe' y el test se colgaba en vez de continuar) -- ahora retoma el login en vez de descartar la cuenta, en los 4 productos. Caveat de ambiente (no de codigo): los 3 CPs que necesitan una cuenta 100% nueva (documento no existente/ya registrado, activacion exitosa) estan skipeando hoy porque el lote de cuentas 'nunca usadas' se agoto y no se repone solo -- no baja el %, es un tema de datos de prueba, ver docs/backlog-automatizacion.md.</t>
+  </si>
+  <si>
+    <t>IMPORTANTE: cada paso por separado SI esta automatizado y pasando (Registracion 100%, Activacion 100%, Compra B2C 50%, Reseteo de contrasena 75% desde 2026-09-06 -- ver fila QA-AUTO-026), pero NINGUN test encadena las 4 etapas en una sola corrida continua -- son specs independientes con cuentas distintas. El 0% refleja el journey end-to-end tal como lo pidio la PO, no la cobertura de las partes.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: tests/projects/vetify-webapp/session.spec.ts TS-01 TC-01 (Cerrar sesion y bloqueo de acceso posterior) cubre logout Y el intento de acceso a seccion protegida tras el logout en un mismo test -- 100% verde, 0 failed. No estaba reflejado en el roadmap (figuraba 0%) pese a ya estar automatizado.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: session.spec.ts TS-02 TC-03 (Persistencia de sesion ante un refresh) -- 100% verde. No estaba reflejado en el roadmap (figuraba 0%) pese a ya estar automatizado.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: session.spec.ts TS-02 TC-02 (Persistencia de sesion entre modulos: Home, Mis Mascotas, Mi Perfil) -- 100% verde. No estaba reflejado en el roadmap (figuraba 0%) pese a ya estar automatizado.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: session.spec.ts TS-02 TC-01 (Acceso directo a ruta protegida sin autenticacion, valida redirect a login con prevPage) -- 100% verde. No estaba reflejado en el roadmap (figuraba 0%) pese a ya estar automatizado.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: tests/projects/vetify-webapp/navigation.spec.ts TS-02 TC-01 (Acceso al mapa de veterinarias, abre modal 'Buscar veterinaria' con mapa embebido) -- 100% verde. El roadmap decia 'gap real, cero CPs' -- ya estaba automatizado.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: navigation.spec.ts TS-02 TC-02 (Busqueda de veterinarias por ubicacion, sugerencias reales al escribir una direccion) -- 100% verde. El roadmap decia 'gap real, cero CPs' -- ya estaba automatizado.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: navigation.spec.ts TS-01 TC-01 (El menu lateral navega correctamente entre Mascotas, Perfil, Reintegros y Planes y coberturas) -- 100% verde. El roadmap decia 'gap real, sin CP dedicado' -- ya estaba automatizado.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: navigation.spec.ts TS-04 Compatibilidad de permisos por plan, TC-01/02/03 (Vetify Plus visible en Adquirente, oculto en OSDE Capitado, Cooper visible en OSDE Capitado) -- 100% verde. El roadmap decia 'gap real, sin CP dedicado' -- ya estaba automatizado.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: tests/projects/vetify-webapp/pets.spec.ts TS-01 TC-01 (Ver el detalle completo de una mascota: nombre, raza, edad, plan asociado, boton bajar credencial) -- 100% verde. El roadmap decia 'gap real, sin CP dedicado' -- ya estaba automatizado.</t>
+  </si>
+  <si>
+    <t>Verificado en vivo 2026-09-07: session.spec.ts TS-03 TC-02 (Tour no reaparece en el segundo login) -- 100% verde. No estaba reflejado en el roadmap (figuraba 0%) pese a ya estar automatizado. Actualizacion 2026-09-07: se agrego ademas el camino alternativo 'Usar camara' (TS-03 TC-02) -- mismo endpoint de subida que el archivo normal, verde y verificado. El sub-CP de 'camara no disponible' (distinto, ver fila de Credencial cargada con errores) no se automatiza: confirmado que la visibilidad de ese boton depende de deteccion real de camara del navegador/SO de la maquina que corre el test, no de la cuenta -- necesitaria mockear navigator.mediaDevices o flags de Playwright, no configurado hoy.</t>
+  </si>
+  <si>
+    <t>Explorado en vivo 2026-09-07: la funcionalidad real de 'Buscar veterinaria' (menu lateral) es un mapa de Google generico centrado en la direccion buscada -- NO hay una lista de veterinarias/prestadores reales cercanas, ni markers de prestadores, ni una tarjeta de detalle para hacer click. No es que falte automatizar el detalle: la pantalla de detalle de un prestador no existe todavia en la UI real. No se automatiza (no hay que fabricar un flujo que no existe). Si en el futuro se agrega un listado real de prestadores, retomar este CP.</t>
+  </si>
+  <si>
+    <t>Explorado en vivo 2026-09-07: confirmados los 15 items reales del menu lateral (SideMenuSection, ya verificados en vivo 2026-08-30) -- no existe ningun item de menu llamado o equivalente a 'Atencion de Red' distinto de los ya cubiertos (Emergencias, Asistencia presencial, Asistencia a domicilio, Historial de Atencion, Veterinarias). Probablemente este CP del roadmap original se solapaba con alguno de esos items ya automatizados bajo otro nombre, no una funcionalidad propia sin construir.</t>
+  </si>
+  <si>
+    <t>Explorado en vivo 2026-09-07: no existe un concepto de 'mascota activa' a nivel de sesion/app en la webapp real -- cada pantalla (Mascotas, Credenciales) simplemente lista todas las mascotas del cliente como tarjetas individuales, no hay un selector que 'cambie el contexto activo' fuera del flujo puntual de Videollamada (donde SI existe un selector, ya cubierto por sus propios CPs de esa HU). No se pudo confirmar visualmente el listado completo con 2+ mascotas por la inestabilidad intermitente ya documentada en BUG-033 (misma cuenta paso de 2 mascotas reales a 0 en menos de 1 minuto entre 2 corridas). No se automatiza: no hay una funcionalidad de 'cambio de mascota activa' propia y separada que probar hoy.</t>
+  </si>
+  <si>
+    <t>Cerrado 2026-09-08: OSDE Adquirente (IMAS-3218) TS-05 verificado en vivo, 4/4 CPs verdes. La causa del bloqueo no era un bug de producto -- era una cuenta de prueba equivocada en el pool de QA (adquirenteosde@gmail.com nunca debio usarse para esto; la cuenta real correcta siempre fue alandgg975@gmail.com). Corregido el dato de prueba, sin cambios de codigo. Los 4 productos (Vetify B2C IMAS-3215, OSDE Capitado IMAS-3216, Flux Capitado IMAS-3217, OSDE Adquirente IMAS-3218) tienen TS-04 y TS-05 100% verdes.</t>
+  </si>
+  <si>
+    <t>CORREGIDO 2026-09-10: era falso positivo del test, no un bug -- newPage.url() nunca se actualiza para una pestana de PDF embebido (limitacion de Playwright con el visor de Chromium), pero el boton SI navega bien (confirmado con click real via MCP, va directo al PDF y responde 200). Test corregido para verificar por la respuesta de red del contexto en vez de Page.url(). 2/2 verde. Ver docs/bugs/BUG-036 (retractado).</t>
+  </si>
+  <si>
+    <t>CORREGIDO 2026-09-10: mismo caso que la fila anterior (BUG-036 retractado, era falso positivo del test). 2/2 verde.</t>
+  </si>
+  <si>
+    <t>RESUELTO 2026-09-10 (IMP-021): se verifica por la respuesta real de red del autocomplete de Google Places (AutocompletionService.GetPredictionsJson, JSONP) en vez de por el iframe cross-origin de Maps -- forzando ZERO_RESULTS con page.route(). 2/2 verde en vivo.</t>
+  </si>
+  <si>
+    <t>ACTUALIZADO 2026-09-10 (IMP-020): solucion tecnica encontrada e implementada -- se intercepta la respuesta real de plans/engage (con reintento por el outage intermitente conocido) forzando pathCondicionado:null en el primer plan real, sin necesitar una cuenta con ese dato exacto en el catalogo. Test escrito y typecheck limpio, pendiente de correr en verde (bloqueado hoy por outage de ambiente afectando el pool de cuentas con plan real). Se mantiene en 0% hasta verificarlo en vivo.</t>
+  </si>
+  <si>
+    <t>Actualizacion 2026-09-10: formalizado como IMP-025 en docs/impedimentos-bloqueos.md (antes vivia sin numero de impedimento ni pedido concreto). El test SI existe (session.spec.ts TS-03 TC-01) pero se confirmo en vivo que esta en rojo de forma consistente (no flaky, reproducido 2 veces) -- regresion causada por la propia migracion a UserSource.Fresh del 2026-09-04 (pensada para otro problema, agotamiento de pool): la activacion de la cuenta Fresh hace un login de cacheo que gasta el unico primer-login que este test necesita, antes de que el test lo vea. Se mantiene en 0% (no en 100%) porque hoy no pasa en vivo. Pedido concreto (IMP-025): decidir entre (a) pool Fresh dedicado sin cacheo de sesion, o (b) volver a Pooled con cuenta virgen real -- ver docs/impedimentos-bloqueos.md.</t>
+  </si>
+  <si>
+    <t>Corregido 2026-09-10: la nota anterior citaba IMP-027 -- ese numero colisionaba con un impedimento real distinto (iOS/BrowserStack) creado el mismo dia en otra parte de la sesion, y ademas la pregunta a Producto era innecesaria: Alan ya habia decidido esto mismo el 2026-09-01 (mantener Automatizable=No de forma permanente, ver qa-workspace/decision-log.md). Sin cambios de fondo: la fila sigue en 0% correctamente, no hay CP escrito, y no hace falta preguntarle a Producto salvo que Alan decida revertir su propia decision.</t>
+  </si>
+  <si>
+    <t>Mismo caso que la fila anterior -- ver nota de QA-AUTO-028.</t>
+  </si>
+  <si>
+    <t>Corregido 2026-09-10: la nota anterior citaba IMP-028 -- innecesario, Alan ya habia decidido esto mismo el 2026-09-01 (mantener Automatizable=No de forma permanente, ver qa-workspace/decision-log.md). Sin cambios de fondo: la fila sigue en 0% correctamente, no hay CP escrito, y no hace falta preguntarle a Producto salvo que Alan decida revertir su propia decision.</t>
+  </si>
+  <si>
+    <t>Mismo caso que la fila anterior -- ver nota de QA-AUTO-071.</t>
+  </si>
+  <si>
+    <t>QA-AUTO-095</t>
+  </si>
+  <si>
+    <t>Condicionados OSDE Adquirente reemplazados (IMAS-4490/4488)</t>
+  </si>
+  <si>
+    <t>Verificar que los 9 planes OSDE Adquirente muestran su nuevo condicionado (PDF) sin ninguna mencion a Vetify Plus, y que Capitado/VET no-OSDE no se vieron afectados.</t>
+  </si>
+  <si>
+    <t>IMP-017, IMP-020</t>
+  </si>
+  <si>
+    <t>11 CPs disenados y verificados manualmente 100% (2026-09-02 a 09-10, ver docs/user-stories/IMAS-4490-prueba-qa-condicionados-osde.tests.md). Automatizado 2026-09-14 (tests/projects/osde-adquirente/condicionados.spec.ts): 3/11 en verde en vivo (CP07 Emergencias x1 OSDE via cuenta pool, CP10 OSDE Capitado regresion, CP11 VET no-OSDE regresion). CP01 (Classic x1 OSDE, cuenta generada fresca) escrito pero bloqueado en vivo por IMP-017 bloqueo-1 (category/overview intermitente), no cuenta como pasando. CP02-06/08/09 (7 planes) test.skip() citando IMP-020 -- el catalogo QA real solo tiene el plan 2358 cargado hoy. No se infla el %: 3/11 = 27%.</t>
   </si>
 </sst>
 </file>
@@ -1590,10 +1623,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.60526315789473684</c:v>
+                  <c:v>0.8421052631578948</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.4</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.7</c:v>
@@ -1605,10 +1638,10 @@
                   <c:v>0.42857142857142855</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.40200000000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.25E-2</c:v>
+                  <c:v>0.10800000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.17857142857142858</c:v>
@@ -1620,7 +1653,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1809,19 +1842,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>48</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2219,7 +2252,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -2270,7 +2303,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="135" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="345" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -2300,10 +2333,10 @@
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="315" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -2333,7 +2366,7 @@
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>305</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2366,7 +2399,7 @@
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="120" x14ac:dyDescent="0.25">
@@ -2399,7 +2432,7 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2432,7 +2465,7 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2465,7 +2498,7 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2498,7 +2531,7 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2531,7 +2564,7 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2564,7 +2597,7 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2597,7 +2630,7 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2630,7 +2663,7 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2663,7 +2696,7 @@
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2696,7 +2729,7 @@
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2729,7 +2762,7 @@
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2762,7 +2795,7 @@
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2795,7 +2828,7 @@
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -2828,7 +2861,7 @@
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2861,7 +2894,7 @@
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2894,10 +2927,10 @@
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="315" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>70</v>
       </c>
@@ -2927,7 +2960,7 @@
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>313</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -2960,7 +2993,7 @@
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -2993,7 +3026,7 @@
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -3026,7 +3059,7 @@
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3059,10 +3092,10 @@
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="135" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>84</v>
       </c>
@@ -3088,11 +3121,11 @@
         <v>1</v>
       </c>
       <c r="I26" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>318</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3125,10 +3158,10 @@
       </c>
       <c r="J27" s="2"/>
       <c r="K27" s="2" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>90</v>
       </c>
@@ -3158,10 +3191,10 @@
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>93</v>
       </c>
@@ -3191,10 +3224,10 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>96</v>
       </c>
@@ -3220,14 +3253,14 @@
         <v>1</v>
       </c>
       <c r="I30" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="150" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>99</v>
       </c>
@@ -3253,14 +3286,14 @@
         <v>1</v>
       </c>
       <c r="I31" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>102</v>
       </c>
@@ -3286,11 +3319,11 @@
         <v>1</v>
       </c>
       <c r="I32" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>324</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -3323,7 +3356,7 @@
       </c>
       <c r="J33" s="2"/>
       <c r="K33" s="2" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="135" x14ac:dyDescent="0.25">
@@ -3356,7 +3389,7 @@
       </c>
       <c r="J34" s="2"/>
       <c r="K34" s="2" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="165" x14ac:dyDescent="0.25">
@@ -3389,10 +3422,10 @@
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>116</v>
       </c>
@@ -3418,14 +3451,14 @@
         <v>1</v>
       </c>
       <c r="I36" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="330" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>119</v>
       </c>
@@ -3455,10 +3488,10 @@
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="345" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>300</v>
       </c>
@@ -3488,10 +3521,10 @@
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="315" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>301</v>
       </c>
@@ -3517,11 +3550,11 @@
         <v>3</v>
       </c>
       <c r="I39" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>326</v>
+        <v>408</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3554,7 +3587,7 @@
       </c>
       <c r="J40" s="2"/>
       <c r="K40" s="2" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -3587,7 +3620,7 @@
       </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -3620,7 +3653,7 @@
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="2" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="240" x14ac:dyDescent="0.25">
@@ -3653,7 +3686,7 @@
       </c>
       <c r="J43" s="2"/>
       <c r="K43" s="2" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3686,7 +3719,7 @@
       </c>
       <c r="J44" s="2"/>
       <c r="K44" s="2" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3719,7 +3752,7 @@
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -3752,7 +3785,7 @@
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3785,7 +3818,7 @@
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3818,7 +3851,7 @@
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="165" x14ac:dyDescent="0.25">
@@ -3851,7 +3884,7 @@
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="135" x14ac:dyDescent="0.25">
@@ -3884,7 +3917,7 @@
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="90" x14ac:dyDescent="0.25">
@@ -3917,7 +3950,7 @@
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3950,7 +3983,7 @@
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3983,7 +4016,7 @@
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -4016,7 +4049,7 @@
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4049,10 +4082,10 @@
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>157</v>
       </c>
@@ -4078,14 +4111,14 @@
         <v>1</v>
       </c>
       <c r="I56" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>161</v>
       </c>
@@ -4111,14 +4144,14 @@
         <v>1</v>
       </c>
       <c r="I57" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="240" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>164</v>
       </c>
@@ -4148,10 +4181,10 @@
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>167</v>
       </c>
@@ -4177,14 +4210,14 @@
         <v>2</v>
       </c>
       <c r="I59" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>170</v>
       </c>
@@ -4214,7 +4247,7 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>349</v>
+        <v>410</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="90" x14ac:dyDescent="0.25">
@@ -4247,10 +4280,10 @@
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="195" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>177</v>
       </c>
@@ -4276,14 +4309,14 @@
         <v>2</v>
       </c>
       <c r="I62" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>180</v>
       </c>
@@ -4309,14 +4342,14 @@
         <v>2</v>
       </c>
       <c r="I63" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>183</v>
       </c>
@@ -4346,7 +4379,7 @@
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>353</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -4379,7 +4412,7 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="150" x14ac:dyDescent="0.25">
@@ -4412,7 +4445,7 @@
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4445,7 +4478,7 @@
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4478,7 +4511,7 @@
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4511,7 +4544,7 @@
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -4544,7 +4577,7 @@
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4577,7 +4610,7 @@
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4610,10 +4643,10 @@
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>212</v>
       </c>
@@ -4643,10 +4676,10 @@
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>215</v>
       </c>
@@ -4676,10 +4709,10 @@
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>219</v>
       </c>
@@ -4705,14 +4738,14 @@
         <v>1</v>
       </c>
       <c r="I75" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>223</v>
       </c>
@@ -4738,11 +4771,11 @@
         <v>1</v>
       </c>
       <c r="I76" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>364</v>
+        <v>405</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="120" x14ac:dyDescent="0.25">
@@ -4771,14 +4804,14 @@
         <v>1</v>
       </c>
       <c r="I77" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="135" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>229</v>
       </c>
@@ -4804,28 +4837,28 @@
         <v>1</v>
       </c>
       <c r="I78" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>364</v>
+        <v>406</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="B79" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C79" t="s">
         <v>45</v>
       </c>
       <c r="D79" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="E79" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="F79" t="s">
         <v>52</v>
@@ -4840,27 +4873,27 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="B80" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C80" t="s">
         <v>45</v>
       </c>
       <c r="D80" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="E80" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="F80" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="G80" t="s">
         <v>16</v>
@@ -4872,27 +4905,27 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="B81" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C81" t="s">
         <v>45</v>
       </c>
       <c r="D81" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="E81" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="F81" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="G81" t="s">
         <v>53</v>
@@ -4904,24 +4937,24 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="B82" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="C82" t="s">
         <v>45</v>
       </c>
       <c r="D82" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="E82" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="F82" t="s">
         <v>15</v>
@@ -4936,24 +4969,24 @@
         <v>100</v>
       </c>
       <c r="K82" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="B83" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="C83" t="s">
         <v>45</v>
       </c>
       <c r="D83" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="E83" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="F83" t="s">
         <v>15</v>
@@ -4968,12 +5001,12 @@
         <v>100</v>
       </c>
       <c r="K83" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="B84" t="s">
         <v>135</v>
@@ -4982,10 +5015,10 @@
         <v>45</v>
       </c>
       <c r="D84" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="E84" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="F84" t="s">
         <v>15</v>
@@ -5000,12 +5033,12 @@
         <v>100</v>
       </c>
       <c r="K84" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="B85" t="s">
         <v>187</v>
@@ -5014,10 +5047,10 @@
         <v>45</v>
       </c>
       <c r="D85" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="E85" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="F85" t="s">
         <v>15</v>
@@ -5032,27 +5065,27 @@
         <v>100</v>
       </c>
       <c r="K85" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="B86" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C86" t="s">
         <v>45</v>
       </c>
       <c r="D86" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="E86" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="F86" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="G86" t="s">
         <v>16</v>
@@ -5064,30 +5097,30 @@
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="K86" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="B87" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C87" t="s">
         <v>45</v>
       </c>
       <c r="D87" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="E87" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="F87" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="G87" t="s">
         <v>16</v>
@@ -5099,15 +5132,15 @@
         <v>0</v>
       </c>
       <c r="J87" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="K87" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>408</v>
+        <v>387</v>
       </c>
       <c r="B88" t="s">
         <v>280</v>
@@ -5116,10 +5149,10 @@
         <v>45</v>
       </c>
       <c r="D88" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="E88" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="F88" t="s">
         <v>15</v>
@@ -5134,12 +5167,12 @@
         <v>100</v>
       </c>
       <c r="K88" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="B89" t="s">
         <v>280</v>
@@ -5148,10 +5181,10 @@
         <v>45</v>
       </c>
       <c r="D89" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="E89" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="F89" t="s">
         <v>15</v>
@@ -5166,7 +5199,42 @@
         <v>100</v>
       </c>
       <c r="K89" t="s">
-        <v>415</v>
+        <v>394</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>422</v>
+      </c>
+      <c r="B90" t="s">
+        <v>174</v>
+      </c>
+      <c r="C90" t="s">
+        <v>18</v>
+      </c>
+      <c r="D90" t="s">
+        <v>423</v>
+      </c>
+      <c r="E90" t="s">
+        <v>424</v>
+      </c>
+      <c r="F90" t="s">
+        <v>15</v>
+      </c>
+      <c r="G90" t="s">
+        <v>16</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+      <c r="I90">
+        <v>27</v>
+      </c>
+      <c r="J90" t="s">
+        <v>425</v>
+      </c>
+      <c r="K90" t="s">
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -5312,19 +5380,19 @@
       <c r="A8" s="7"/>
       <c r="B8" s="20">
         <f>COUNTA('Roadmap QA Automation'!A2:A1998)</f>
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="7"/>
       <c r="E8" s="21">
         <f>IFERROR(AVERAGE('Roadmap QA Automation'!I2:I1998)/100,0)</f>
-        <v>0.40340909090909094</v>
+        <v>0.53146067415730336</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="7"/>
       <c r="H8" s="19">
         <f>COUNTIF('Roadmap QA Automation'!I2:I1998,100)</f>
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="I8" s="18"/>
       <c r="J8" s="7"/>
@@ -5448,7 +5516,7 @@
       </c>
       <c r="D16" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B16,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.60526315789473684</v>
+        <v>0.8421052631578948</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -5468,7 +5536,7 @@
       </c>
       <c r="D17" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B17,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -5548,7 +5616,7 @@
       </c>
       <c r="D21" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B21,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -5564,11 +5632,11 @@
       </c>
       <c r="C22" s="7">
         <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B22,3)&amp;"*")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B22,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>6.25E-2</v>
+        <v>0.10800000000000001</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -5648,7 +5716,7 @@
       </c>
       <c r="D26" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!B:B,LEFT(B26,3)&amp;"*",'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -5660,7 +5728,7 @@
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="C27" s="7">
         <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B27,3)&amp;"*")</f>
@@ -5680,7 +5748,7 @@
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="7" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="C28" s="7">
         <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B28,3)&amp;"*")</f>
@@ -5700,7 +5768,7 @@
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="7" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C29" s="7">
         <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B29,3)&amp;"*")</f>
@@ -5754,7 +5822,7 @@
       </c>
       <c r="C32" s="7">
         <f>COUNTIF('Roadmap QA Automation'!I:I,0)</f>
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -5788,7 +5856,7 @@
       </c>
       <c r="C34" s="7">
         <f>COUNTIF('Roadmap QA Automation'!I:I,50)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -5822,7 +5890,7 @@
       </c>
       <c r="C36" s="7">
         <f>COUNTIF('Roadmap QA Automation'!I:I,100)</f>
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -5907,11 +5975,11 @@
       </c>
       <c r="C42" s="7">
         <f>COUNTIF('Roadmap QA Automation'!G:G,B42)</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D42" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!G:G,B42,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.39615384615384613</v>
+        <v>0.55333333333333334</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
@@ -5931,7 +5999,7 @@
       </c>
       <c r="D43" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!G:G,B43,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.46052631578947367</v>
+        <v>0.46210526315789474</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
@@ -5951,7 +6019,7 @@
       </c>
       <c r="D44" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!G:G,B44,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -6043,11 +6111,11 @@
       </c>
       <c r="C50" s="7">
         <f>COUNTIF('Roadmap QA Automation'!C:C,B50)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D50" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!C:C,B50,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.16666666666666669</v>
+        <v>0.1925</v>
       </c>
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
@@ -6107,7 +6175,7 @@
       </c>
       <c r="D53" s="11">
         <f>IFERROR(AVERAGEIF('Roadmap QA Automation'!C:C,B53,'Roadmap QA Automation'!I:I)/100,0)</f>
-        <v>0.40714285714285714</v>
+        <v>0.57185714285714284</v>
       </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>

--- a/documentation/Automation Vetify.xlsx
+++ b/documentation/Automation Vetify.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ike\vetify-automation\automation\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C64C5346-3ABC-4244-A1BD-17512FAEABDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9793EC78-D72A-4036-9A63-F7129BC8F175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1010,9 +1010,6 @@
     <t>Hoja Credenciales, TS-02, subconjunto de errores (columna Automatizado Desktop): fecha futura (No), camara no disponible (No), camara disponible (No -- limitacion real de dispositivo, no gap de automatizacion), formato invalido (Si), imagen demasiado grande (Si). 2/5 CPs en desktop. Aparte: el mismo caso de imagen demasiado grande tiene un test MOBILE escrito el 2026-08-29 pero todavia sin verificar en vivo (columna Automatizado Mobile de esta misma hoja sigue en No) -- no afecta este numero, que es solo desktop.</t>
   </si>
   <si>
-    <t>Hoja Videollamadas, combinando IMAS-3899 (5 de 5, bloqueo sin credencial), IMAS-3174 (8 de 8, flujo 1 mascota), IMAS-3889 (17 de 18, multi-mascota y adjuntos, unico No es un caso de bypass de validacion directo a API), IMAS-3909 (4 de 4, limites de turnos) e IMAS-4023 (4 de 4, errores de carga de archivo, excluyendo 1 CP marcado Fuera de alcance). 38 de 39 CPs.</t>
-  </si>
-  <si>
     <t>Los 2 CPs relacionados (IMAS-3894 CP05 y CP06) estan marcados explicitamente como Brecha de cobertura y Fuera de alcance en Casos de Prueba.xlsx -- salir de la videoconsulta (sala de espera, ingreso y salida) fue una decision ya tomada de no automatizar, no un gap pendiente de priorizar.</t>
   </si>
   <si>
@@ -1320,6 +1317,9 @@
   </si>
   <si>
     <t>11 CPs disenados y verificados manualmente 100% (2026-09-02 a 09-10, ver docs/user-stories/IMAS-4490-prueba-qa-condicionados-osde.tests.md). Automatizado 2026-09-14 (tests/projects/osde-adquirente/condicionados.spec.ts): 3/11 en verde en vivo (CP07 Emergencias x1 OSDE via cuenta pool, CP10 OSDE Capitado regresion, CP11 VET no-OSDE regresion). CP01 (Classic x1 OSDE, cuenta generada fresca) escrito pero bloqueado en vivo por IMP-017 bloqueo-1 (category/overview intermitente), no cuenta como pasando. CP02-06/08/09 (7 planes) test.skip() citando IMP-020 -- el catalogo QA real solo tiene el plan 2358 cargado hoy. No se infla el %: 3/11 = 27%.</t>
+  </si>
+  <si>
+    <t>Hoja Videollamadas, combinando IMAS-3899 (5 de 5, bloqueo sin credencial), IMAS-3174 (8 de 8, flujo 1 mascota), IMAS-3889 (17 de 18, multi-mascota y adjuntos, unico No es un caso de bypass de validacion directo a API), IMAS-3909 (4 de 4, limites de turnos), IMAS-4023 (4 de 4, errores de carga de archivo, excluyendo 1 CP marcado Fuera de alcance) e IMAS-4546 (5 de 5 CPs criticos - cupo parametrizable por plan, contador Cupo disponible X de Y, modal nuevo de cupo anual agotado, cancelacion restituye cupo, aislamiento multi-mascota; excluye CP06 Caso especial 04 -plan sin videollamada-, brecha de cobertura no critica, pendiente de dato real del dev). 43 de 45 CPs.</t>
   </si>
 </sst>
 </file>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="315" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2729,7 +2729,7 @@
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="J28" s="2"/>
       <c r="K28" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="J29" s="2"/>
       <c r="K29" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="150" x14ac:dyDescent="0.25">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="J30" s="2"/>
       <c r="K30" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="150" x14ac:dyDescent="0.25">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="J31" s="2"/>
       <c r="K31" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="90" x14ac:dyDescent="0.25">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="J32" s="2"/>
       <c r="K32" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="J35" s="2"/>
       <c r="K35" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="120" x14ac:dyDescent="0.25">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="J36" s="2"/>
       <c r="K36" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="330" x14ac:dyDescent="0.25">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="345" x14ac:dyDescent="0.25">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="J38" s="2"/>
       <c r="K38" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="315" x14ac:dyDescent="0.25">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="J39" s="2"/>
       <c r="K39" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="J45" s="2"/>
       <c r="K45" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="J46" s="2"/>
       <c r="K46" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -3851,10 +3851,10 @@
       </c>
       <c r="J48" s="2"/>
       <c r="K48" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="165" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="285" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>138</v>
       </c>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="J49" s="2"/>
       <c r="K49" s="2" t="s">
-        <v>323</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="135" x14ac:dyDescent="0.25">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="J50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="90" x14ac:dyDescent="0.25">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="J51" s="2"/>
       <c r="K51" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="J53" s="2"/>
       <c r="K53" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="J54" s="2"/>
       <c r="K54" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="J55" s="2"/>
       <c r="K55" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="120" x14ac:dyDescent="0.25">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="J56" s="2"/>
       <c r="K56" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="J57" s="2"/>
       <c r="K57" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="240" x14ac:dyDescent="0.25">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="J58" s="2"/>
       <c r="K58" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="120" x14ac:dyDescent="0.25">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="90" x14ac:dyDescent="0.25">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="J61" s="2"/>
       <c r="K61" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="195" x14ac:dyDescent="0.25">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="J62" s="2"/>
       <c r="K62" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="J63" s="2"/>
       <c r="K63" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="225" x14ac:dyDescent="0.25">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="150" x14ac:dyDescent="0.25">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="J66" s="2"/>
       <c r="K66" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="J67" s="2"/>
       <c r="K67" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="J68" s="2"/>
       <c r="K68" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="J71" s="2"/>
       <c r="K71" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="45" x14ac:dyDescent="0.25">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="J72" s="2"/>
       <c r="K72" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="165" x14ac:dyDescent="0.25">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="J73" s="2"/>
       <c r="K73" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="30" x14ac:dyDescent="0.25">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="120" x14ac:dyDescent="0.25">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="J77" s="2"/>
       <c r="K77" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="135" x14ac:dyDescent="0.25">
@@ -4841,24 +4841,24 @@
       </c>
       <c r="J78" s="2"/>
       <c r="K78" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>344</v>
+      </c>
+      <c r="B79" t="s">
         <v>345</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" t="s">
         <v>346</v>
       </c>
-      <c r="C79" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>347</v>
-      </c>
-      <c r="E79" t="s">
-        <v>348</v>
       </c>
       <c r="F79" t="s">
         <v>52</v>
@@ -4873,27 +4873,27 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>349</v>
+      </c>
+      <c r="B80" t="s">
+        <v>345</v>
+      </c>
+      <c r="C80" t="s">
+        <v>45</v>
+      </c>
+      <c r="D80" t="s">
         <v>350</v>
       </c>
-      <c r="B80" t="s">
-        <v>346</v>
-      </c>
-      <c r="C80" t="s">
-        <v>45</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>351</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>352</v>
-      </c>
-      <c r="F80" t="s">
-        <v>353</v>
       </c>
       <c r="G80" t="s">
         <v>16</v>
@@ -4905,27 +4905,27 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>354</v>
+      </c>
+      <c r="B81" t="s">
+        <v>345</v>
+      </c>
+      <c r="C81" t="s">
+        <v>45</v>
+      </c>
+      <c r="D81" t="s">
         <v>355</v>
       </c>
-      <c r="B81" t="s">
-        <v>346</v>
-      </c>
-      <c r="C81" t="s">
-        <v>45</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
         <v>356</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>357</v>
-      </c>
-      <c r="F81" t="s">
-        <v>358</v>
       </c>
       <c r="G81" t="s">
         <v>53</v>
@@ -4937,24 +4937,24 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>359</v>
+      </c>
+      <c r="B82" t="s">
         <v>360</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" t="s">
         <v>361</v>
       </c>
-      <c r="C82" t="s">
-        <v>45</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>362</v>
-      </c>
-      <c r="E82" t="s">
-        <v>363</v>
       </c>
       <c r="F82" t="s">
         <v>15</v>
@@ -4969,24 +4969,24 @@
         <v>100</v>
       </c>
       <c r="K82" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>364</v>
+      </c>
+      <c r="B83" t="s">
+        <v>360</v>
+      </c>
+      <c r="C83" t="s">
+        <v>45</v>
+      </c>
+      <c r="D83" t="s">
         <v>365</v>
       </c>
-      <c r="B83" t="s">
-        <v>361</v>
-      </c>
-      <c r="C83" t="s">
-        <v>45</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>366</v>
-      </c>
-      <c r="E83" t="s">
-        <v>367</v>
       </c>
       <c r="F83" t="s">
         <v>15</v>
@@ -5001,12 +5001,12 @@
         <v>100</v>
       </c>
       <c r="K83" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B84" t="s">
         <v>135</v>
@@ -5015,10 +5015,10 @@
         <v>45</v>
       </c>
       <c r="D84" t="s">
+        <v>369</v>
+      </c>
+      <c r="E84" t="s">
         <v>370</v>
-      </c>
-      <c r="E84" t="s">
-        <v>371</v>
       </c>
       <c r="F84" t="s">
         <v>15</v>
@@ -5033,12 +5033,12 @@
         <v>100</v>
       </c>
       <c r="K84" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B85" t="s">
         <v>187</v>
@@ -5047,10 +5047,10 @@
         <v>45</v>
       </c>
       <c r="D85" t="s">
+        <v>373</v>
+      </c>
+      <c r="E85" t="s">
         <v>374</v>
-      </c>
-      <c r="E85" t="s">
-        <v>375</v>
       </c>
       <c r="F85" t="s">
         <v>15</v>
@@ -5065,27 +5065,27 @@
         <v>100</v>
       </c>
       <c r="K85" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>376</v>
+      </c>
+      <c r="B86" t="s">
         <v>377</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
+        <v>45</v>
+      </c>
+      <c r="D86" t="s">
         <v>378</v>
       </c>
-      <c r="C86" t="s">
-        <v>45</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>379</v>
       </c>
-      <c r="E86" t="s">
-        <v>380</v>
-      </c>
       <c r="F86" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G86" t="s">
         <v>16</v>
@@ -5097,30 +5097,30 @@
         <v>0</v>
       </c>
       <c r="J86" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K86" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>381</v>
+      </c>
+      <c r="B87" t="s">
+        <v>377</v>
+      </c>
+      <c r="C87" t="s">
+        <v>45</v>
+      </c>
+      <c r="D87" t="s">
         <v>382</v>
       </c>
-      <c r="B87" t="s">
-        <v>378</v>
-      </c>
-      <c r="C87" t="s">
-        <v>45</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>383</v>
       </c>
-      <c r="E87" t="s">
-        <v>384</v>
-      </c>
       <c r="F87" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G87" t="s">
         <v>16</v>
@@ -5132,15 +5132,15 @@
         <v>0</v>
       </c>
       <c r="J87" t="s">
+        <v>384</v>
+      </c>
+      <c r="K87" t="s">
         <v>385</v>
-      </c>
-      <c r="K87" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B88" t="s">
         <v>280</v>
@@ -5149,10 +5149,10 @@
         <v>45</v>
       </c>
       <c r="D88" t="s">
+        <v>387</v>
+      </c>
+      <c r="E88" t="s">
         <v>388</v>
-      </c>
-      <c r="E88" t="s">
-        <v>389</v>
       </c>
       <c r="F88" t="s">
         <v>15</v>
@@ -5167,12 +5167,12 @@
         <v>100</v>
       </c>
       <c r="K88" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B89" t="s">
         <v>280</v>
@@ -5181,10 +5181,10 @@
         <v>45</v>
       </c>
       <c r="D89" t="s">
+        <v>391</v>
+      </c>
+      <c r="E89" t="s">
         <v>392</v>
-      </c>
-      <c r="E89" t="s">
-        <v>393</v>
       </c>
       <c r="F89" t="s">
         <v>15</v>
@@ -5199,12 +5199,12 @@
         <v>100</v>
       </c>
       <c r="K89" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B90" t="s">
         <v>174</v>
@@ -5213,10 +5213,10 @@
         <v>18</v>
       </c>
       <c r="D90" t="s">
+        <v>422</v>
+      </c>
+      <c r="E90" t="s">
         <v>423</v>
-      </c>
-      <c r="E90" t="s">
-        <v>424</v>
       </c>
       <c r="F90" t="s">
         <v>15</v>
@@ -5231,10 +5231,10 @@
         <v>27</v>
       </c>
       <c r="J90" t="s">
+        <v>424</v>
+      </c>
+      <c r="K90" t="s">
         <v>425</v>
-      </c>
-      <c r="K90" t="s">
-        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -5728,7 +5728,7 @@
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="7"/>
       <c r="B27" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C27" s="7">
         <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B27,3)&amp;"*")</f>
@@ -5748,7 +5748,7 @@
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="7"/>
       <c r="B28" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C28" s="7">
         <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B28,3)&amp;"*")</f>
@@ -5768,7 +5768,7 @@
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
       <c r="B29" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C29" s="7">
         <f>COUNTIF('Roadmap QA Automation'!B:B,LEFT(B29,3)&amp;"*")</f>
@@ -6323,26 +6323,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="823bb257-b027-4d06-8b2f-053335b328b1" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101009F842B2145328244B4B47741AC555AE2" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="783508ae003506b91aa2be35b4ebc887">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e" xmlns:ns3="823bb257-b027-4d06-8b2f-053335b328b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4b965eb5b8ebcdb894d7355c785d1653" ns2:_="" ns3:_="">
     <xsd:import namespace="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e"/>
@@ -6537,26 +6517,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{347876AB-BDAE-4A3D-A9BF-1638E774D861}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e"/>
-    <ds:schemaRef ds:uri="823bb257-b027-4d06-8b2f-053335b328b1"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{211C9EF2-99F3-47CC-A9EA-437B32406790}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="823bb257-b027-4d06-8b2f-053335b328b1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A512D99-C2FC-42B8-8FDB-89CED4284B88}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6573,4 +6554,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{211C9EF2-99F3-47CC-A9EA-437B32406790}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{347876AB-BDAE-4A3D-A9BF-1638E774D861}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96ffd99d-26d2-4d99-98b0-05d0b9b7ac4e"/>
+    <ds:schemaRef ds:uri="823bb257-b027-4d06-8b2f-053335b328b1"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>